--- a/research/traditional_assets/database/data/germany/germany_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_drugs_biotechnology.xlsx
@@ -2629,7 +2629,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2766,22 +2766,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09555508507731092</v>
+        <v>0.09529991982207897</v>
       </c>
       <c r="C2">
-        <v>13.02754057021206</v>
+        <v>12.90762736730347</v>
       </c>
       <c r="D2">
-        <v>11.73754057021206</v>
+        <v>11.75208244269855</v>
       </c>
       <c r="E2">
-        <v>-12.43550753950755</v>
+        <v>-12.30105246411247</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1344550753950755</v>
       </c>
       <c r="G2">
         <v>1.29</v>
@@ -2802,28 +2802,28 @@
         <v>3.008</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.006763090292372295</v>
       </c>
       <c r="N2">
-        <v>3.008</v>
+        <v>3.001236909707628</v>
       </c>
       <c r="O2">
-        <v>0.9024</v>
+        <v>0.9003710729122884</v>
       </c>
       <c r="P2">
-        <v>2.1056</v>
+        <v>2.100865836795339</v>
       </c>
       <c r="Q2">
-        <v>2.7216</v>
+        <v>2.71686583679534</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09555508507731092</v>
+        <v>0.09590688870917069</v>
       </c>
       <c r="T2">
-        <v>1.149078177305102</v>
+        <v>1.157202972498169</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>444.7670916640803</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2848,22 +2848,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09529991982207897</v>
+        <v>0.09504475456684705</v>
       </c>
       <c r="C3">
-        <v>12.90762736730347</v>
+        <v>12.78775024152171</v>
       </c>
       <c r="D3">
-        <v>11.75208244269855</v>
+        <v>11.76666039231186</v>
       </c>
       <c r="E3">
-        <v>-12.30105246411247</v>
+        <v>-12.1665973887174</v>
       </c>
       <c r="F3">
-        <v>0.1344550753950755</v>
+        <v>0.2689101507901509</v>
       </c>
       <c r="G3">
         <v>1.29</v>
@@ -2884,28 +2884,28 @@
         <v>3.008</v>
       </c>
       <c r="M3">
-        <v>0.006763090292372295</v>
+        <v>0.01352618058474459</v>
       </c>
       <c r="N3">
-        <v>3.001236909707628</v>
+        <v>2.994473819415255</v>
       </c>
       <c r="O3">
-        <v>0.9003710729122884</v>
+        <v>0.8983421458245766</v>
       </c>
       <c r="P3">
-        <v>2.100865836795339</v>
+        <v>2.096131673590679</v>
       </c>
       <c r="Q3">
-        <v>2.71686583679534</v>
+        <v>2.712131673590679</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09590688870917069</v>
+        <v>0.09626587200698679</v>
       </c>
       <c r="T3">
-        <v>1.157202972498169</v>
+        <v>1.165493579838032</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>444.7670916640803</v>
+        <v>222.3835458320401</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2930,22 +2930,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09504475456684705</v>
+        <v>0.09478958931161512</v>
       </c>
       <c r="C4">
-        <v>12.78775024152171</v>
+        <v>12.66790932728987</v>
       </c>
       <c r="D4">
-        <v>11.76666039231186</v>
+        <v>11.78127455347509</v>
       </c>
       <c r="E4">
-        <v>-12.1665973887174</v>
+        <v>-12.03214231332232</v>
       </c>
       <c r="F4">
-        <v>0.2689101507901509</v>
+        <v>0.4033652261852264</v>
       </c>
       <c r="G4">
         <v>1.29</v>
@@ -2966,28 +2966,28 @@
         <v>3.008</v>
       </c>
       <c r="M4">
-        <v>0.01352618058474459</v>
+        <v>0.02028927087711688</v>
       </c>
       <c r="N4">
-        <v>2.994473819415255</v>
+        <v>2.987710729122883</v>
       </c>
       <c r="O4">
-        <v>0.8983421458245766</v>
+        <v>0.896313218736865</v>
       </c>
       <c r="P4">
-        <v>2.096131673590679</v>
+        <v>2.091397510386019</v>
       </c>
       <c r="Q4">
-        <v>2.712131673590679</v>
+        <v>2.707397510386019</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09626587200698679</v>
+        <v>0.09663225702228363</v>
       </c>
       <c r="T4">
-        <v>1.165493579838032</v>
+        <v>1.173955127535419</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>222.3835458320401</v>
+        <v>148.2556972213601</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -3012,22 +3012,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09478958931161512</v>
+        <v>0.0945344240563832</v>
       </c>
       <c r="C5">
-        <v>12.66790932728987</v>
+        <v>12.54810475969967</v>
       </c>
       <c r="D5">
-        <v>11.78127455347509</v>
+        <v>11.79592506127998</v>
       </c>
       <c r="E5">
-        <v>-12.03214231332232</v>
+        <v>-11.89768723792724</v>
       </c>
       <c r="F5">
-        <v>0.4033652261852264</v>
+        <v>0.5378203015803018</v>
       </c>
       <c r="G5">
         <v>1.29</v>
@@ -3048,28 +3048,28 @@
         <v>3.008</v>
       </c>
       <c r="M5">
-        <v>0.02028927087711688</v>
+        <v>0.02705236116948918</v>
       </c>
       <c r="N5">
-        <v>2.987710729122883</v>
+        <v>2.980947638830511</v>
       </c>
       <c r="O5">
-        <v>0.896313218736865</v>
+        <v>0.8942842916491532</v>
       </c>
       <c r="P5">
-        <v>2.091397510386019</v>
+        <v>2.086663347181358</v>
       </c>
       <c r="Q5">
-        <v>2.707397510386019</v>
+        <v>2.702663347181358</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09663225702228363</v>
+        <v>0.09700627505873249</v>
       </c>
       <c r="T5">
-        <v>1.173955127535419</v>
+        <v>1.182592957476501</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -3086,7 +3086,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>148.2556972213601</v>
+        <v>111.1917729160201</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -3094,22 +3094,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0945344240563832</v>
+        <v>0.09427925880115125</v>
       </c>
       <c r="C6">
-        <v>12.54810475969967</v>
+        <v>12.42833667451567</v>
       </c>
       <c r="D6">
-        <v>11.79592506127998</v>
+        <v>11.81061205149105</v>
       </c>
       <c r="E6">
-        <v>-11.89768723792724</v>
+        <v>-11.76323216253217</v>
       </c>
       <c r="F6">
-        <v>0.5378203015803018</v>
+        <v>0.6722753769753773</v>
       </c>
       <c r="G6">
         <v>1.29</v>
@@ -3130,28 +3130,28 @@
         <v>3.008</v>
       </c>
       <c r="M6">
-        <v>0.02705236116948918</v>
+        <v>0.03381545146186148</v>
       </c>
       <c r="N6">
-        <v>2.980947638830511</v>
+        <v>2.974184548538139</v>
       </c>
       <c r="O6">
-        <v>0.8942842916491532</v>
+        <v>0.8922553645614416</v>
       </c>
       <c r="P6">
-        <v>2.086663347181358</v>
+        <v>2.081929183976697</v>
       </c>
       <c r="Q6">
-        <v>2.702663347181358</v>
+        <v>2.697929183976697</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09700627505873249</v>
+        <v>0.09738816715910659</v>
       </c>
       <c r="T6">
-        <v>1.182592957476501</v>
+        <v>1.191412636468974</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>111.1917729160201</v>
+        <v>88.95341833281606</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -3176,22 +3176,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09427925880115125</v>
+        <v>0.09402409354591933</v>
       </c>
       <c r="C7">
-        <v>12.42833667451567</v>
+        <v>12.30860520817939</v>
       </c>
       <c r="D7">
-        <v>11.81061205149105</v>
+        <v>11.82533566054984</v>
       </c>
       <c r="E7">
-        <v>-11.76323216253217</v>
+        <v>-11.62877708713709</v>
       </c>
       <c r="F7">
-        <v>0.6722753769753773</v>
+        <v>0.8067304523704528</v>
       </c>
       <c r="G7">
         <v>1.29</v>
@@ -3212,28 +3212,28 @@
         <v>3.008</v>
       </c>
       <c r="M7">
-        <v>0.03381545146186148</v>
+        <v>0.04057854175423378</v>
       </c>
       <c r="N7">
-        <v>2.974184548538139</v>
+        <v>2.967421458245766</v>
       </c>
       <c r="O7">
-        <v>0.8922553645614416</v>
+        <v>0.8902264374737298</v>
       </c>
       <c r="P7">
-        <v>2.081929183976697</v>
+        <v>2.077195020772036</v>
       </c>
       <c r="Q7">
-        <v>2.697929183976697</v>
+        <v>2.693195020772036</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09738816715910659</v>
+        <v>0.09777818462331843</v>
       </c>
       <c r="T7">
-        <v>1.191412636468974</v>
+        <v>1.200419968205968</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>88.95341833281606</v>
+        <v>74.12784861068003</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -3258,22 +3258,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09402409354591933</v>
+        <v>0.09376892829068739</v>
       </c>
       <c r="C8">
-        <v>12.30860520817939</v>
+        <v>12.18891049781359</v>
       </c>
       <c r="D8">
-        <v>11.82533566054984</v>
+        <v>11.84009602557912</v>
       </c>
       <c r="E8">
-        <v>-11.62877708713709</v>
+        <v>-11.49432201174202</v>
       </c>
       <c r="F8">
-        <v>0.8067304523704527</v>
+        <v>0.9411855277655281</v>
       </c>
       <c r="G8">
         <v>1.29</v>
@@ -3294,28 +3294,28 @@
         <v>3.008</v>
       </c>
       <c r="M8">
-        <v>0.04057854175423377</v>
+        <v>0.04734163204660606</v>
       </c>
       <c r="N8">
-        <v>2.967421458245766</v>
+        <v>2.960658367953394</v>
       </c>
       <c r="O8">
-        <v>0.8902264374737298</v>
+        <v>0.8881975103860181</v>
       </c>
       <c r="P8">
-        <v>2.077195020772036</v>
+        <v>2.072460857567376</v>
       </c>
       <c r="Q8">
-        <v>2.693195020772036</v>
+        <v>2.688460857567376</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09777818462331843</v>
+        <v>0.09817658955987892</v>
       </c>
       <c r="T8">
-        <v>1.200419968205968</v>
+        <v>1.209621006001823</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>74.12784861068005</v>
+        <v>63.53815595201147</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -3340,22 +3340,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09376892829068739</v>
+        <v>0.09351376303545546</v>
       </c>
       <c r="C9">
-        <v>12.18891049781359</v>
+        <v>12.06925268122652</v>
       </c>
       <c r="D9">
-        <v>11.84009602557912</v>
+        <v>11.85489328438712</v>
       </c>
       <c r="E9">
-        <v>-11.49432201174202</v>
+        <v>-11.35986693634694</v>
       </c>
       <c r="F9">
-        <v>0.9411855277655282</v>
+        <v>1.075640603160604</v>
       </c>
       <c r="G9">
         <v>1.29</v>
@@ -3376,28 +3376,28 @@
         <v>3.008</v>
       </c>
       <c r="M9">
-        <v>0.04734163204660607</v>
+        <v>0.05410472233897836</v>
       </c>
       <c r="N9">
-        <v>2.960658367953394</v>
+        <v>2.953895277661021</v>
       </c>
       <c r="O9">
-        <v>0.8881975103860181</v>
+        <v>0.8861685832983064</v>
       </c>
       <c r="P9">
-        <v>2.072460857567376</v>
+        <v>2.067726694362715</v>
       </c>
       <c r="Q9">
-        <v>2.688460857567376</v>
+        <v>2.683726694362715</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09817658955987892</v>
+        <v>0.09858365547332115</v>
       </c>
       <c r="T9">
-        <v>1.209621006001823</v>
+        <v>1.219022066358456</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>63.53815595201146</v>
+        <v>55.59588645801003</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -3422,22 +3422,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09351376303545546</v>
+        <v>0.09325859778022354</v>
       </c>
       <c r="C10">
-        <v>12.06925268122652</v>
+        <v>11.94963189691619</v>
       </c>
       <c r="D10">
-        <v>11.85489328438712</v>
+        <v>11.86972757547187</v>
       </c>
       <c r="E10">
-        <v>-11.35986693634694</v>
+        <v>-11.22541186095187</v>
       </c>
       <c r="F10">
-        <v>1.075640603160604</v>
+        <v>1.210095678555679</v>
       </c>
       <c r="G10">
         <v>1.29</v>
@@ -3458,28 +3458,28 @@
         <v>3.008</v>
       </c>
       <c r="M10">
-        <v>0.05410472233897836</v>
+        <v>0.06086781263135066</v>
       </c>
       <c r="N10">
-        <v>2.953895277661021</v>
+        <v>2.947132187368649</v>
       </c>
       <c r="O10">
-        <v>0.8861685832983064</v>
+        <v>0.8841396562105948</v>
       </c>
       <c r="P10">
-        <v>2.067726694362715</v>
+        <v>2.062992531158055</v>
       </c>
       <c r="Q10">
-        <v>2.683726694362715</v>
+        <v>2.678992531158055</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09858365547332115</v>
+        <v>0.09899966789035552</v>
       </c>
       <c r="T10">
-        <v>1.219022066358456</v>
+        <v>1.228629743426225</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>55.59588645801003</v>
+        <v>49.41856574045336</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -3504,22 +3504,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09325859778022354</v>
+        <v>0.09300343252499157</v>
       </c>
       <c r="C11">
-        <v>11.94963189691619</v>
+        <v>11.8300482840747</v>
       </c>
       <c r="D11">
-        <v>11.86972757547187</v>
+        <v>11.88459903802546</v>
       </c>
       <c r="E11">
-        <v>-11.22541186095187</v>
+        <v>-11.09095678555679</v>
       </c>
       <c r="F11">
-        <v>1.210095678555679</v>
+        <v>1.344550753950754</v>
       </c>
       <c r="G11">
         <v>1.29</v>
@@ -3540,28 +3540,28 @@
         <v>3.008</v>
       </c>
       <c r="M11">
-        <v>0.06086781263135066</v>
+        <v>0.06763090292372294</v>
       </c>
       <c r="N11">
-        <v>2.947132187368649</v>
+        <v>2.940369097076277</v>
       </c>
       <c r="O11">
-        <v>0.8841396562105948</v>
+        <v>0.8821107291228831</v>
       </c>
       <c r="P11">
-        <v>2.062992531158055</v>
+        <v>2.058258367953394</v>
       </c>
       <c r="Q11">
-        <v>2.678992531158055</v>
+        <v>2.674258367953394</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09899966789035552</v>
+        <v>0.09942492502776842</v>
       </c>
       <c r="T11">
-        <v>1.228629743426225</v>
+        <v>1.238450924428832</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>49.41856574045336</v>
+        <v>44.47670916640804</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -3586,22 +3586,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09300343252499157</v>
+        <v>0.09274826726975967</v>
       </c>
       <c r="C12">
-        <v>11.8300482840747</v>
+        <v>11.71050198259261</v>
       </c>
       <c r="D12">
-        <v>11.88459903802546</v>
+        <v>11.89950781193844</v>
       </c>
       <c r="E12">
-        <v>-11.09095678555679</v>
+        <v>-10.95650171016172</v>
       </c>
       <c r="F12">
-        <v>1.344550753950755</v>
+        <v>1.47900582934583</v>
       </c>
       <c r="G12">
         <v>1.29</v>
@@ -3622,28 +3622,28 @@
         <v>3.008</v>
       </c>
       <c r="M12">
-        <v>0.06763090292372295</v>
+        <v>0.07439399321609524</v>
       </c>
       <c r="N12">
-        <v>2.940369097076277</v>
+        <v>2.933606006783905</v>
       </c>
       <c r="O12">
-        <v>0.8821107291228831</v>
+        <v>0.8800818020351714</v>
       </c>
       <c r="P12">
-        <v>2.058258367953394</v>
+        <v>2.053524204748733</v>
       </c>
       <c r="Q12">
-        <v>2.674258367953394</v>
+        <v>2.669524204748734</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09942492502776842</v>
+        <v>0.09985973850534793</v>
       </c>
       <c r="T12">
-        <v>1.238450924428832</v>
+        <v>1.248492806128128</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>44.47670916640803</v>
+        <v>40.43337196946185</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -3668,22 +3668,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09274826726975967</v>
+        <v>0.09249310201452773</v>
       </c>
       <c r="C13">
-        <v>11.71050198259261</v>
+        <v>11.59099313306328</v>
       </c>
       <c r="D13">
-        <v>11.89950781193844</v>
+        <v>11.91445403780419</v>
       </c>
       <c r="E13">
-        <v>-10.95650171016172</v>
+        <v>-10.82204663476664</v>
       </c>
       <c r="F13">
-        <v>1.47900582934583</v>
+        <v>1.613460904740905</v>
       </c>
       <c r="G13">
         <v>1.29</v>
@@ -3704,28 +3704,28 @@
         <v>3.008</v>
       </c>
       <c r="M13">
-        <v>0.07439399321609524</v>
+        <v>0.08115708350846754</v>
       </c>
       <c r="N13">
-        <v>2.933606006783905</v>
+        <v>2.926842916491533</v>
       </c>
       <c r="O13">
-        <v>0.8800818020351714</v>
+        <v>0.8780528749474598</v>
       </c>
       <c r="P13">
-        <v>2.053524204748733</v>
+        <v>2.048790041544073</v>
       </c>
       <c r="Q13">
-        <v>2.669524204748734</v>
+        <v>2.664790041544073</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09985973850534793</v>
+        <v>0.1003044341074179</v>
       </c>
       <c r="T13">
-        <v>1.248492806128128</v>
+        <v>1.258762912411498</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>40.43337196946185</v>
+        <v>37.06392430534002</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3750,22 +3750,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09249310201452773</v>
+        <v>0.09223793675929581</v>
       </c>
       <c r="C14">
-        <v>11.59099313306328</v>
+        <v>11.47152187678736</v>
       </c>
       <c r="D14">
-        <v>11.91445403780419</v>
+        <v>11.92943785692334</v>
       </c>
       <c r="E14">
-        <v>-10.82204663476664</v>
+        <v>-10.68759155937157</v>
       </c>
       <c r="F14">
-        <v>1.613460904740905</v>
+        <v>1.747915980135981</v>
       </c>
       <c r="G14">
         <v>1.29</v>
@@ -3786,28 +3786,28 @@
         <v>3.008</v>
       </c>
       <c r="M14">
-        <v>0.08115708350846754</v>
+        <v>0.08792017380083984</v>
       </c>
       <c r="N14">
-        <v>2.926842916491533</v>
+        <v>2.92007982619916</v>
       </c>
       <c r="O14">
-        <v>0.8780528749474598</v>
+        <v>0.876023947859748</v>
       </c>
       <c r="P14">
-        <v>2.048790041544073</v>
+        <v>2.044055878339412</v>
       </c>
       <c r="Q14">
-        <v>2.664790041544073</v>
+        <v>2.660055878339412</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1003044341074179</v>
+        <v>0.1007593525968917</v>
       </c>
       <c r="T14">
-        <v>1.258762912411498</v>
+        <v>1.269269113092188</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>37.06392430534002</v>
+        <v>34.21285320492925</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -3832,22 +3832,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09223793675929581</v>
+        <v>0.09198277150406386</v>
       </c>
       <c r="C15">
-        <v>11.47152187678736</v>
+        <v>11.35208835577717</v>
       </c>
       <c r="D15">
-        <v>11.92943785692334</v>
+        <v>11.94445941130822</v>
       </c>
       <c r="E15">
-        <v>-10.68759155937157</v>
+        <v>-10.55313648397649</v>
       </c>
       <c r="F15">
-        <v>1.747915980135981</v>
+        <v>1.882371055531056</v>
       </c>
       <c r="G15">
         <v>1.29</v>
@@ -3868,28 +3868,28 @@
         <v>3.008</v>
       </c>
       <c r="M15">
-        <v>0.08792017380083984</v>
+        <v>0.09468326409321214</v>
       </c>
       <c r="N15">
-        <v>2.92007982619916</v>
+        <v>2.913316735906788</v>
       </c>
       <c r="O15">
-        <v>0.876023947859748</v>
+        <v>0.8739950207720364</v>
       </c>
       <c r="P15">
-        <v>2.044055878339412</v>
+        <v>2.039321715134752</v>
       </c>
       <c r="Q15">
-        <v>2.660055878339412</v>
+        <v>2.655321715134752</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1007593525968917</v>
+        <v>0.1012248505861208</v>
       </c>
       <c r="T15">
-        <v>1.269269113092188</v>
+        <v>1.280019644021265</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>34.21285320492925</v>
+        <v>31.76907797600573</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3914,22 +3914,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09198277150406386</v>
+        <v>0.09172760624883193</v>
       </c>
       <c r="C16">
-        <v>11.35208835577717</v>
+        <v>11.23269271276123</v>
       </c>
       <c r="D16">
-        <v>11.94445941130822</v>
+        <v>11.95951884368737</v>
       </c>
       <c r="E16">
-        <v>-10.55313648397649</v>
+        <v>-10.41868140858141</v>
       </c>
       <c r="F16">
-        <v>1.882371055531056</v>
+        <v>2.016826130926132</v>
       </c>
       <c r="G16">
         <v>1.29</v>
@@ -3950,28 +3950,28 @@
         <v>3.008</v>
       </c>
       <c r="M16">
-        <v>0.09468326409321214</v>
+        <v>0.1014463543855844</v>
       </c>
       <c r="N16">
-        <v>2.913316735906788</v>
+        <v>2.906553645614415</v>
       </c>
       <c r="O16">
-        <v>0.8739950207720364</v>
+        <v>0.8719660936843247</v>
       </c>
       <c r="P16">
-        <v>2.039321715134752</v>
+        <v>2.034587551930091</v>
       </c>
       <c r="Q16">
-        <v>2.655321715134752</v>
+        <v>2.650587551930091</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1012248505861208</v>
+        <v>0.1017013014692141</v>
       </c>
       <c r="T16">
-        <v>1.280019644021265</v>
+        <v>1.291023128619262</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>31.76907797600573</v>
+        <v>29.65113944427201</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3996,22 +3996,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09172760624883193</v>
+        <v>0.0914724409936</v>
       </c>
       <c r="C17">
-        <v>11.23269271276123</v>
+        <v>11.11333509118879</v>
       </c>
       <c r="D17">
-        <v>11.95951884368737</v>
+        <v>11.97461629751</v>
       </c>
       <c r="E17">
-        <v>-10.41868140858141</v>
+        <v>-10.28422633318634</v>
       </c>
       <c r="F17">
-        <v>2.016826130926132</v>
+        <v>2.151281206321207</v>
       </c>
       <c r="G17">
         <v>1.29</v>
@@ -4032,28 +4032,28 @@
         <v>3.008</v>
       </c>
       <c r="M17">
-        <v>0.1014463543855844</v>
+        <v>0.1082094446779567</v>
       </c>
       <c r="N17">
-        <v>2.906553645614415</v>
+        <v>2.899790555322043</v>
       </c>
       <c r="O17">
-        <v>0.8719660936843247</v>
+        <v>0.869937166596613</v>
       </c>
       <c r="P17">
-        <v>2.034587551930091</v>
+        <v>2.02985338872543</v>
       </c>
       <c r="Q17">
-        <v>2.650587551930091</v>
+        <v>2.64585338872543</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1017013014692141</v>
+        <v>0.1021890964209524</v>
       </c>
       <c r="T17">
-        <v>1.291023128619262</v>
+        <v>1.302288600945782</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>29.65113944427202</v>
+        <v>27.79794322900502</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -4078,22 +4078,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0914724409936</v>
+        <v>0.09121727573836806</v>
       </c>
       <c r="C18">
-        <v>11.11333509118879</v>
+        <v>10.99401563523434</v>
       </c>
       <c r="D18">
-        <v>11.97461629751</v>
+        <v>11.98975191695062</v>
       </c>
       <c r="E18">
-        <v>-10.28422633318634</v>
+        <v>-10.14977125779126</v>
       </c>
       <c r="F18">
-        <v>2.151281206321207</v>
+        <v>2.285736281716283</v>
       </c>
       <c r="G18">
         <v>1.29</v>
@@ -4114,28 +4114,28 @@
         <v>3.008</v>
       </c>
       <c r="M18">
-        <v>0.1082094446779567</v>
+        <v>0.114972534970329</v>
       </c>
       <c r="N18">
-        <v>2.899790555322043</v>
+        <v>2.893027465029671</v>
       </c>
       <c r="O18">
-        <v>0.869937166596613</v>
+        <v>0.8679082395089012</v>
       </c>
       <c r="P18">
-        <v>2.02985338872543</v>
+        <v>2.02511922552077</v>
       </c>
       <c r="Q18">
-        <v>2.64585338872543</v>
+        <v>2.64111922552077</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1021890964209524</v>
+        <v>0.1026886454679133</v>
       </c>
       <c r="T18">
-        <v>1.302288600945782</v>
+        <v>1.313825530436798</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>27.79794322900502</v>
+        <v>26.16277009788707</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -4160,22 +4160,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09121727573836806</v>
+        <v>0.09096211048313613</v>
       </c>
       <c r="C19">
-        <v>10.99401563523434</v>
+        <v>10.87473448980222</v>
       </c>
       <c r="D19">
-        <v>11.98975191695062</v>
+        <v>12.00492584691358</v>
       </c>
       <c r="E19">
-        <v>-10.14977125779126</v>
+        <v>-10.01531618239619</v>
       </c>
       <c r="F19">
-        <v>2.285736281716283</v>
+        <v>2.420191357111358</v>
       </c>
       <c r="G19">
         <v>1.29</v>
@@ -4196,28 +4196,28 @@
         <v>3.008</v>
       </c>
       <c r="M19">
-        <v>0.114972534970329</v>
+        <v>0.1217356252627013</v>
       </c>
       <c r="N19">
-        <v>2.893027465029671</v>
+        <v>2.886264374737299</v>
       </c>
       <c r="O19">
-        <v>0.8679082395089012</v>
+        <v>0.8658793124211895</v>
       </c>
       <c r="P19">
-        <v>2.02511922552077</v>
+        <v>2.020385062316109</v>
       </c>
       <c r="Q19">
-        <v>2.64111922552077</v>
+        <v>2.636385062316109</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1026886454679133</v>
+        <v>0.1032003786379709</v>
       </c>
       <c r="T19">
-        <v>1.313825530436798</v>
+        <v>1.325643848451984</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>26.16277009788707</v>
+        <v>24.70928287022668</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -4242,22 +4242,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09096211048313614</v>
+        <v>0.09070694522790421</v>
       </c>
       <c r="C20">
-        <v>10.87473448980222</v>
+        <v>10.75549180053127</v>
       </c>
       <c r="D20">
-        <v>12.00492584691358</v>
+        <v>12.02013823303771</v>
       </c>
       <c r="E20">
-        <v>-10.01531618239619</v>
+        <v>-9.880861107001111</v>
       </c>
       <c r="F20">
-        <v>2.420191357111358</v>
+        <v>2.554646432506434</v>
       </c>
       <c r="G20">
         <v>1.29</v>
@@ -4278,28 +4278,28 @@
         <v>3.008</v>
       </c>
       <c r="M20">
-        <v>0.1217356252627013</v>
+        <v>0.1284987155550736</v>
       </c>
       <c r="N20">
-        <v>2.886264374737299</v>
+        <v>2.879501284444927</v>
       </c>
       <c r="O20">
-        <v>0.8658793124211895</v>
+        <v>0.8638503853334779</v>
       </c>
       <c r="P20">
-        <v>2.020385062316109</v>
+        <v>2.015650899111449</v>
       </c>
       <c r="Q20">
-        <v>2.636385062316109</v>
+        <v>2.631650899111449</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1032003786379709</v>
+        <v>0.1037247471949435</v>
       </c>
       <c r="T20">
-        <v>1.325643848451984</v>
+        <v>1.337753976788532</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>24.70928287022668</v>
+        <v>23.40879429810949</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -4324,22 +4324,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09070694522790421</v>
+        <v>0.09045177997267229</v>
       </c>
       <c r="C21">
-        <v>10.75549180053127</v>
+        <v>10.63628771379948</v>
       </c>
       <c r="D21">
-        <v>12.02013823303771</v>
+        <v>12.03538922170098</v>
       </c>
       <c r="E21">
-        <v>-9.880861107001111</v>
+        <v>-9.746406031606035</v>
       </c>
       <c r="F21">
-        <v>2.554646432506434</v>
+        <v>2.689101507901509</v>
       </c>
       <c r="G21">
         <v>1.29</v>
@@ -4360,28 +4360,28 @@
         <v>3.008</v>
       </c>
       <c r="M21">
-        <v>0.1284987155550736</v>
+        <v>0.1352618058474459</v>
       </c>
       <c r="N21">
-        <v>2.879501284444927</v>
+        <v>2.872738194152554</v>
       </c>
       <c r="O21">
-        <v>0.8638503853334779</v>
+        <v>0.8618214582457662</v>
       </c>
       <c r="P21">
-        <v>2.015650899111449</v>
+        <v>2.010916735906788</v>
       </c>
       <c r="Q21">
-        <v>2.631650899111449</v>
+        <v>2.626916735906788</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1037247471949435</v>
+        <v>0.1042622249658403</v>
       </c>
       <c r="T21">
-        <v>1.337753976788532</v>
+        <v>1.350166858333495</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>23.40879429810949</v>
+        <v>22.23835458320401</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -4406,22 +4406,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09045177997267229</v>
+        <v>0.09019661471744034</v>
       </c>
       <c r="C22">
-        <v>10.63628771379948</v>
+        <v>10.51712237672862</v>
       </c>
       <c r="D22">
-        <v>12.03538922170098</v>
+        <v>12.05067896002521</v>
       </c>
       <c r="E22">
-        <v>-9.746406031606035</v>
+        <v>-9.611950956210961</v>
       </c>
       <c r="F22">
-        <v>2.689101507901509</v>
+        <v>2.823556583296585</v>
       </c>
       <c r="G22">
         <v>1.29</v>
@@ -4442,28 +4442,28 @@
         <v>3.008</v>
       </c>
       <c r="M22">
-        <v>0.1352618058474459</v>
+        <v>0.1420248961398182</v>
       </c>
       <c r="N22">
-        <v>2.872738194152554</v>
+        <v>2.865975103860182</v>
       </c>
       <c r="O22">
-        <v>0.8618214582457662</v>
+        <v>0.8597925311580545</v>
       </c>
       <c r="P22">
-        <v>2.010916735906788</v>
+        <v>2.006182572702127</v>
       </c>
       <c r="Q22">
-        <v>2.626916735906788</v>
+        <v>2.622182572702128</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1042622249658403</v>
+        <v>0.1048133097689118</v>
       </c>
       <c r="T22">
-        <v>1.350166858333495</v>
+        <v>1.362893990044153</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>22.23835458320401</v>
+        <v>21.17938531733716</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -4488,22 +4488,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09019661471744034</v>
+        <v>0.0899414494622084</v>
       </c>
       <c r="C23">
-        <v>10.51712237672862</v>
+        <v>10.39799593718908</v>
       </c>
       <c r="D23">
-        <v>12.05067896002521</v>
+        <v>12.06600759588074</v>
       </c>
       <c r="E23">
-        <v>-9.611950956210961</v>
+        <v>-9.477495880815885</v>
       </c>
       <c r="F23">
-        <v>2.823556583296584</v>
+        <v>2.95801165869166</v>
       </c>
       <c r="G23">
         <v>1.29</v>
@@ -4524,28 +4524,28 @@
         <v>3.008</v>
       </c>
       <c r="M23">
-        <v>0.1420248961398182</v>
+        <v>0.1487879864321905</v>
       </c>
       <c r="N23">
-        <v>2.865975103860182</v>
+        <v>2.859212013567809</v>
       </c>
       <c r="O23">
-        <v>0.8597925311580545</v>
+        <v>0.8577636040703428</v>
       </c>
       <c r="P23">
-        <v>2.006182572702127</v>
+        <v>2.001448409497466</v>
       </c>
       <c r="Q23">
-        <v>2.622182572702128</v>
+        <v>2.617448409497467</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1048133097689118</v>
+        <v>0.1053785249515492</v>
       </c>
       <c r="T23">
-        <v>1.362893990044153</v>
+        <v>1.37594745846534</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>21.17938531733716</v>
+        <v>20.21668598473092</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -4570,22 +4570,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0899414494622084</v>
+        <v>0.08968628420697647</v>
       </c>
       <c r="C24">
-        <v>10.39799593718908</v>
+        <v>10.27890854380455</v>
       </c>
       <c r="D24">
-        <v>12.06600759588074</v>
+        <v>12.08137527789129</v>
       </c>
       <c r="E24">
-        <v>-9.477495880815885</v>
+        <v>-9.343040805420809</v>
       </c>
       <c r="F24">
-        <v>2.95801165869166</v>
+        <v>3.092466734086736</v>
       </c>
       <c r="G24">
         <v>1.29</v>
@@ -4606,28 +4606,28 @@
         <v>3.008</v>
       </c>
       <c r="M24">
-        <v>0.1487879864321905</v>
+        <v>0.1555510767245628</v>
       </c>
       <c r="N24">
-        <v>2.859212013567809</v>
+        <v>2.852448923275437</v>
       </c>
       <c r="O24">
-        <v>0.8577636040703428</v>
+        <v>0.8557346769826312</v>
       </c>
       <c r="P24">
-        <v>2.001448409497466</v>
+        <v>1.996714246292806</v>
       </c>
       <c r="Q24">
-        <v>2.617448409497467</v>
+        <v>2.612714246292806</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1053785249515492</v>
+        <v>0.1059584210480214</v>
       </c>
       <c r="T24">
-        <v>1.37594745846534</v>
+        <v>1.389339978014351</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -4644,7 +4644,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>20.21668598473092</v>
+        <v>19.3376996375687</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -4652,22 +4652,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08968628420697647</v>
+        <v>0.08943111895174453</v>
       </c>
       <c r="C25">
-        <v>10.27890854380455</v>
+        <v>10.15986034595687</v>
       </c>
       <c r="D25">
-        <v>12.08137527789129</v>
+        <v>12.09678215543868</v>
       </c>
       <c r="E25">
-        <v>-9.343040805420809</v>
+        <v>-9.208585730025735</v>
       </c>
       <c r="F25">
-        <v>3.092466734086736</v>
+        <v>3.226921809481811</v>
       </c>
       <c r="G25">
         <v>1.29</v>
@@ -4688,28 +4688,28 @@
         <v>3.008</v>
       </c>
       <c r="M25">
-        <v>0.1555510767245628</v>
+        <v>0.1623141670169351</v>
       </c>
       <c r="N25">
-        <v>2.852448923275437</v>
+        <v>2.845685832983065</v>
       </c>
       <c r="O25">
-        <v>0.8557346769826312</v>
+        <v>0.8537057498949194</v>
       </c>
       <c r="P25">
-        <v>1.996714246292806</v>
+        <v>1.991980083088145</v>
       </c>
       <c r="Q25">
-        <v>2.612714246292806</v>
+        <v>2.607980083088145</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1059584210480214</v>
+        <v>0.1065535775680849</v>
       </c>
       <c r="T25">
-        <v>1.389339978014351</v>
+        <v>1.403084932288335</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>19.3376996375687</v>
+        <v>18.53196215267001</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -4734,22 +4734,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08943111895174453</v>
+        <v>0.08917595369651261</v>
       </c>
       <c r="C26">
-        <v>10.15986034595687</v>
+        <v>10.04085149379084</v>
       </c>
       <c r="D26">
-        <v>12.09678215543868</v>
+        <v>12.11222837866773</v>
       </c>
       <c r="E26">
-        <v>-9.208585730025735</v>
+        <v>-9.074130654630659</v>
       </c>
       <c r="F26">
-        <v>3.226921809481811</v>
+        <v>3.361376884876886</v>
       </c>
       <c r="G26">
         <v>1.29</v>
@@ -4770,28 +4770,28 @@
         <v>3.008</v>
       </c>
       <c r="M26">
-        <v>0.1623141670169351</v>
+        <v>0.1690772573093074</v>
       </c>
       <c r="N26">
-        <v>2.845685832983065</v>
+        <v>2.838922742690693</v>
       </c>
       <c r="O26">
-        <v>0.8537057498949194</v>
+        <v>0.8516768228072078</v>
       </c>
       <c r="P26">
-        <v>1.991980083088145</v>
+        <v>1.987245919883485</v>
       </c>
       <c r="Q26">
-        <v>2.607980083088145</v>
+        <v>2.603245919883485</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1065535775680849</v>
+        <v>0.1071646049286835</v>
       </c>
       <c r="T26">
-        <v>1.403084932288335</v>
+        <v>1.417196418676293</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>18.53196215267001</v>
+        <v>17.79068366656321</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -4816,22 +4816,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08917595369651261</v>
+        <v>0.08892078844128067</v>
       </c>
       <c r="C27">
-        <v>10.04085149379084</v>
+        <v>9.921882138219123</v>
       </c>
       <c r="D27">
-        <v>12.11222837866773</v>
+        <v>12.12771409849109</v>
       </c>
       <c r="E27">
-        <v>-9.074130654630659</v>
+        <v>-8.939675579235583</v>
       </c>
       <c r="F27">
-        <v>3.361376884876886</v>
+        <v>3.495831960271962</v>
       </c>
       <c r="G27">
         <v>1.29</v>
@@ -4852,28 +4852,28 @@
         <v>3.008</v>
       </c>
       <c r="M27">
-        <v>0.1690772573093074</v>
+        <v>0.1758403476016797</v>
       </c>
       <c r="N27">
-        <v>2.838922742690693</v>
+        <v>2.83215965239832</v>
       </c>
       <c r="O27">
-        <v>0.8516768228072078</v>
+        <v>0.8496478957194961</v>
       </c>
       <c r="P27">
-        <v>1.987245919883485</v>
+        <v>1.982511756678824</v>
       </c>
       <c r="Q27">
-        <v>2.603245919883485</v>
+        <v>2.598511756678824</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1071646049286835</v>
+        <v>0.1077921465422712</v>
       </c>
       <c r="T27">
-        <v>1.417196418676293</v>
+        <v>1.431689296588249</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>17.79068366656321</v>
+        <v>17.10642660246462</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4898,22 +4898,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08892078844128067</v>
+        <v>0.08866562318604873</v>
       </c>
       <c r="C28">
-        <v>9.921882138219123</v>
+        <v>9.802952430927149</v>
       </c>
       <c r="D28">
-        <v>12.12771409849109</v>
+        <v>12.14323946659419</v>
       </c>
       <c r="E28">
-        <v>-8.939675579235583</v>
+        <v>-8.805220503840509</v>
       </c>
       <c r="F28">
-        <v>3.495831960271962</v>
+        <v>3.630287035667037</v>
       </c>
       <c r="G28">
         <v>1.29</v>
@@ -4934,28 +4934,28 @@
         <v>3.008</v>
       </c>
       <c r="M28">
-        <v>0.1758403476016797</v>
+        <v>0.182603437894052</v>
       </c>
       <c r="N28">
-        <v>2.83215965239832</v>
+        <v>2.825396562105948</v>
       </c>
       <c r="O28">
-        <v>0.8496478957194961</v>
+        <v>0.8476189686317844</v>
       </c>
       <c r="P28">
-        <v>1.982511756678824</v>
+        <v>1.977777593474164</v>
       </c>
       <c r="Q28">
-        <v>2.598511756678824</v>
+        <v>2.593777593474164</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1077921465422712</v>
+        <v>0.1084368810767791</v>
       </c>
       <c r="T28">
-        <v>1.431689296588249</v>
+        <v>1.446579239648478</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>17.10642660246462</v>
+        <v>16.47285524681779</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4980,22 +4980,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08866562318604873</v>
+        <v>0.0884104579308168</v>
       </c>
       <c r="C29">
-        <v>9.802952430927149</v>
+        <v>9.684062524378064</v>
       </c>
       <c r="D29">
-        <v>12.14323946659419</v>
+        <v>12.15880463544018</v>
       </c>
       <c r="E29">
-        <v>-8.805220503840509</v>
+        <v>-8.670765428445433</v>
       </c>
       <c r="F29">
-        <v>3.630287035667037</v>
+        <v>3.764742111062113</v>
       </c>
       <c r="G29">
         <v>1.29</v>
@@ -5016,28 +5016,28 @@
         <v>3.008</v>
       </c>
       <c r="M29">
-        <v>0.182603437894052</v>
+        <v>0.1893665281864243</v>
       </c>
       <c r="N29">
-        <v>2.825396562105948</v>
+        <v>2.818633471813576</v>
       </c>
       <c r="O29">
-        <v>0.8476189686317844</v>
+        <v>0.8455900415440728</v>
       </c>
       <c r="P29">
-        <v>1.977777593474164</v>
+        <v>1.973043430269503</v>
       </c>
       <c r="Q29">
-        <v>2.593777593474164</v>
+        <v>2.589043430269503</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1084368810767791</v>
+        <v>0.1090995249039122</v>
       </c>
       <c r="T29">
-        <v>1.446579239648478</v>
+        <v>1.461882792238158</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>16.47285524681779</v>
+        <v>15.88453898800287</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -5062,22 +5062,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0884104579308168</v>
+        <v>0.08815529267558486</v>
       </c>
       <c r="C30">
-        <v>9.684062524378064</v>
+        <v>9.565212571817723</v>
       </c>
       <c r="D30">
-        <v>12.15880463544018</v>
+        <v>12.17440975827491</v>
       </c>
       <c r="E30">
-        <v>-8.670765428445433</v>
+        <v>-8.536310353050357</v>
       </c>
       <c r="F30">
-        <v>3.764742111062113</v>
+        <v>3.899197186457189</v>
       </c>
       <c r="G30">
         <v>1.29</v>
@@ -5098,28 +5098,28 @@
         <v>3.008</v>
       </c>
       <c r="M30">
-        <v>0.1893665281864243</v>
+        <v>0.1961296184787966</v>
       </c>
       <c r="N30">
-        <v>2.818633471813576</v>
+        <v>2.811870381521203</v>
       </c>
       <c r="O30">
-        <v>0.8455900415440728</v>
+        <v>0.8435611144563609</v>
       </c>
       <c r="P30">
-        <v>1.973043430269503</v>
+        <v>1.968309267064842</v>
       </c>
       <c r="Q30">
-        <v>2.589043430269503</v>
+        <v>2.584309267064842</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1090995249039122</v>
+        <v>0.1097808347543449</v>
       </c>
       <c r="T30">
-        <v>1.461882792238158</v>
+        <v>1.477617430816279</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>15.88453898800287</v>
+        <v>15.33679626427863</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -5144,22 +5144,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08815529267558486</v>
+        <v>0.08790012742035294</v>
       </c>
       <c r="C31">
-        <v>9.565212571817723</v>
+        <v>9.446402727279725</v>
       </c>
       <c r="D31">
-        <v>12.17440975827491</v>
+        <v>12.19005498913199</v>
       </c>
       <c r="E31">
-        <v>-8.536310353050357</v>
+        <v>-8.401855277655283</v>
       </c>
       <c r="F31">
-        <v>3.899197186457188</v>
+        <v>4.033652261852263</v>
       </c>
       <c r="G31">
         <v>1.29</v>
@@ -5180,28 +5180,28 @@
         <v>3.008</v>
       </c>
       <c r="M31">
-        <v>0.1961296184787965</v>
+        <v>0.2028927087711688</v>
       </c>
       <c r="N31">
-        <v>2.811870381521203</v>
+        <v>2.805107291228831</v>
       </c>
       <c r="O31">
-        <v>0.8435611144563609</v>
+        <v>0.8415321873686493</v>
       </c>
       <c r="P31">
-        <v>1.968309267064842</v>
+        <v>1.963575103860182</v>
       </c>
       <c r="Q31">
-        <v>2.584309267064842</v>
+        <v>2.579575103860182</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1097808347543449</v>
+        <v>0.1104816106005042</v>
       </c>
       <c r="T31">
-        <v>1.477617430816279</v>
+        <v>1.493801630496633</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>15.33679626427863</v>
+        <v>14.82556972213601</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -5226,22 +5226,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08790012742035294</v>
+        <v>0.08764496216512099</v>
       </c>
       <c r="C32">
-        <v>9.446402727279725</v>
+        <v>9.327633145590482</v>
       </c>
       <c r="D32">
-        <v>12.19005498913199</v>
+        <v>12.20574048283782</v>
       </c>
       <c r="E32">
-        <v>-8.401855277655283</v>
+        <v>-8.267400202260205</v>
       </c>
       <c r="F32">
-        <v>4.033652261852263</v>
+        <v>4.168107337247339</v>
       </c>
       <c r="G32">
         <v>1.29</v>
@@ -5262,28 +5262,28 @@
         <v>3.008</v>
       </c>
       <c r="M32">
-        <v>0.2028927087711688</v>
+        <v>0.2096557990635411</v>
       </c>
       <c r="N32">
-        <v>2.805107291228831</v>
+        <v>2.798344200936459</v>
       </c>
       <c r="O32">
-        <v>0.8415321873686493</v>
+        <v>0.8395032602809376</v>
       </c>
       <c r="P32">
-        <v>1.963575103860182</v>
+        <v>1.958840940655521</v>
       </c>
       <c r="Q32">
-        <v>2.579575103860182</v>
+        <v>2.574840940655521</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1104816106005042</v>
+        <v>0.1112026987900304</v>
       </c>
       <c r="T32">
-        <v>1.493801630496633</v>
+        <v>1.510454937414098</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -5300,7 +5300,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>14.82556972213601</v>
+        <v>14.34732553755098</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -5308,22 +5308,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08764496216512099</v>
+        <v>0.08738979690988907</v>
       </c>
       <c r="C33">
-        <v>9.327633145590482</v>
+        <v>9.208903982374304</v>
       </c>
       <c r="D33">
-        <v>12.20574048283782</v>
+        <v>12.22146639501672</v>
       </c>
       <c r="E33">
-        <v>-8.267400202260205</v>
+        <v>-8.132945126865131</v>
       </c>
       <c r="F33">
-        <v>4.168107337247339</v>
+        <v>4.302562412642414</v>
       </c>
       <c r="G33">
         <v>1.29</v>
@@ -5344,28 +5344,28 @@
         <v>3.008</v>
       </c>
       <c r="M33">
-        <v>0.2096557990635411</v>
+        <v>0.2164188893559134</v>
       </c>
       <c r="N33">
-        <v>2.798344200936459</v>
+        <v>2.791581110644087</v>
       </c>
       <c r="O33">
-        <v>0.8395032602809376</v>
+        <v>0.837474333193226</v>
       </c>
       <c r="P33">
-        <v>1.958840940655521</v>
+        <v>1.954106777450861</v>
       </c>
       <c r="Q33">
-        <v>2.574840940655521</v>
+        <v>2.570106777450861</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1112026987900304</v>
+        <v>0.1119449954557192</v>
       </c>
       <c r="T33">
-        <v>1.510454937414098</v>
+        <v>1.527598047476195</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>14.34732553755098</v>
+        <v>13.89897161450251</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -5390,22 +5390,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08738979690988907</v>
+        <v>0.08713463165465714</v>
       </c>
       <c r="C34">
-        <v>9.208903982374304</v>
+        <v>9.090215394058575</v>
       </c>
       <c r="D34">
-        <v>12.22146639501672</v>
+        <v>12.23723288209607</v>
       </c>
       <c r="E34">
-        <v>-8.132945126865131</v>
+        <v>-7.998490051470055</v>
       </c>
       <c r="F34">
-        <v>4.302562412642414</v>
+        <v>4.43701748803749</v>
       </c>
       <c r="G34">
         <v>1.29</v>
@@ -5426,28 +5426,28 @@
         <v>3.008</v>
       </c>
       <c r="M34">
-        <v>0.2164188893559134</v>
+        <v>0.2231819796482858</v>
       </c>
       <c r="N34">
-        <v>2.791581110644087</v>
+        <v>2.784818020351714</v>
       </c>
       <c r="O34">
-        <v>0.837474333193226</v>
+        <v>0.8354454061055142</v>
       </c>
       <c r="P34">
-        <v>1.954106777450861</v>
+        <v>1.9493726142462</v>
       </c>
       <c r="Q34">
-        <v>2.570106777450861</v>
+        <v>2.5653726142462</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1119449954557192</v>
+        <v>0.1127094502308316</v>
       </c>
       <c r="T34">
-        <v>1.527598047476195</v>
+        <v>1.545252892167011</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>13.89897161450251</v>
+        <v>13.47779065648728</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -5472,22 +5472,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08713463165465714</v>
+        <v>0.0868794663994252</v>
       </c>
       <c r="C35">
-        <v>9.090215394058575</v>
+        <v>8.971567537878936</v>
       </c>
       <c r="D35">
-        <v>12.23723288209607</v>
+        <v>12.2530401013115</v>
       </c>
       <c r="E35">
-        <v>-7.998490051470055</v>
+        <v>-7.86403497607498</v>
       </c>
       <c r="F35">
-        <v>4.43701748803749</v>
+        <v>4.571472563432565</v>
       </c>
       <c r="G35">
         <v>1.29</v>
@@ -5508,28 +5508,28 @@
         <v>3.008</v>
       </c>
       <c r="M35">
-        <v>0.2231819796482858</v>
+        <v>0.229945069940658</v>
       </c>
       <c r="N35">
-        <v>2.784818020351714</v>
+        <v>2.778054930059342</v>
       </c>
       <c r="O35">
-        <v>0.8354454061055142</v>
+        <v>0.8334164790178026</v>
       </c>
       <c r="P35">
-        <v>1.9493726142462</v>
+        <v>1.94463845104154</v>
       </c>
       <c r="Q35">
-        <v>2.5653726142462</v>
+        <v>2.56063845104154</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1127094502308316</v>
+        <v>0.1134970703021594</v>
       </c>
       <c r="T35">
-        <v>1.545252892167011</v>
+        <v>1.563442732151487</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>13.47779065648728</v>
+        <v>13.08138504894354</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -5554,22 +5554,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0868794663994252</v>
+        <v>0.08699180114419326</v>
       </c>
       <c r="C36">
-        <v>8.971567537878936</v>
+        <v>8.830148414284889</v>
       </c>
       <c r="D36">
-        <v>12.2530401013115</v>
+        <v>12.24607605311253</v>
       </c>
       <c r="E36">
-        <v>-7.86403497607498</v>
+        <v>-7.729579900679904</v>
       </c>
       <c r="F36">
-        <v>4.571472563432565</v>
+        <v>4.705927638827641</v>
       </c>
       <c r="G36">
         <v>1.29</v>
@@ -5590,45 +5590,45 @@
         <v>3.008</v>
       </c>
       <c r="M36">
-        <v>0.229945069940658</v>
+        <v>0.2437670516912718</v>
       </c>
       <c r="N36">
-        <v>2.778054930059342</v>
+        <v>2.764232948308728</v>
       </c>
       <c r="O36">
-        <v>0.8334164790178026</v>
+        <v>0.8292698844926184</v>
       </c>
       <c r="P36">
-        <v>1.94463845104154</v>
+        <v>1.93496306381611</v>
       </c>
       <c r="Q36">
-        <v>2.56063845104154</v>
+        <v>2.55096306381611</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1134970703021594</v>
+        <v>0.1143089248372204</v>
       </c>
       <c r="T36">
-        <v>1.563442732151487</v>
+        <v>1.582192259520102</v>
       </c>
       <c r="U36">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y36">
-        <v>13.08138504894354</v>
+        <v>12.33964959222462</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -5636,22 +5636,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08699180114419326</v>
+        <v>0.08674713588896132</v>
       </c>
       <c r="C37">
-        <v>8.830148414284889</v>
+        <v>8.710871214771899</v>
       </c>
       <c r="D37">
-        <v>12.24607605311253</v>
+        <v>12.26125392899462</v>
       </c>
       <c r="E37">
-        <v>-7.729579900679904</v>
+        <v>-7.595124825284829</v>
       </c>
       <c r="F37">
-        <v>4.705927638827641</v>
+        <v>4.840382714222716</v>
       </c>
       <c r="G37">
         <v>1.29</v>
@@ -5672,28 +5672,28 @@
         <v>3.008</v>
       </c>
       <c r="M37">
-        <v>0.2437670516912718</v>
+        <v>0.2507318245967367</v>
       </c>
       <c r="N37">
-        <v>2.764232948308728</v>
+        <v>2.757268175403263</v>
       </c>
       <c r="O37">
-        <v>0.8292698844926184</v>
+        <v>0.8271804526209789</v>
       </c>
       <c r="P37">
-        <v>1.93496306381611</v>
+        <v>1.930087722782284</v>
       </c>
       <c r="Q37">
-        <v>2.55096306381611</v>
+        <v>2.546087722782284</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1143089248372204</v>
+        <v>0.1151461498265021</v>
       </c>
       <c r="T37">
-        <v>1.582192259520102</v>
+        <v>1.601527709618986</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -5710,7 +5710,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>12.33964959222462</v>
+        <v>11.99688154799616</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -5718,22 +5718,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08674713588896134</v>
+        <v>0.0865024706337294</v>
       </c>
       <c r="C38">
-        <v>8.710871214771895</v>
+        <v>8.591631685087069</v>
       </c>
       <c r="D38">
-        <v>12.26125392899461</v>
+        <v>12.27646947470486</v>
       </c>
       <c r="E38">
-        <v>-7.595124825284829</v>
+        <v>-7.460669749889754</v>
       </c>
       <c r="F38">
-        <v>4.840382714222716</v>
+        <v>4.974837789617792</v>
       </c>
       <c r="G38">
         <v>1.29</v>
@@ -5754,28 +5754,28 @@
         <v>3.008</v>
       </c>
       <c r="M38">
-        <v>0.2507318245967367</v>
+        <v>0.2576965975022016</v>
       </c>
       <c r="N38">
-        <v>2.757268175403263</v>
+        <v>2.750303402497798</v>
       </c>
       <c r="O38">
-        <v>0.8271804526209789</v>
+        <v>0.8250910207493395</v>
       </c>
       <c r="P38">
-        <v>1.930087722782284</v>
+        <v>1.925212381748459</v>
       </c>
       <c r="Q38">
-        <v>2.546087722782284</v>
+        <v>2.541212381748459</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1151461498265021</v>
+        <v>0.1160099533868721</v>
       </c>
       <c r="T38">
-        <v>1.601527709618986</v>
+        <v>1.621476983530533</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.99688154799616</v>
+        <v>11.67264150615843</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -5800,22 +5800,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0865024706337294</v>
+        <v>0.08625780537849746</v>
       </c>
       <c r="C39">
-        <v>8.591631685087069</v>
+        <v>8.472429965643233</v>
       </c>
       <c r="D39">
-        <v>12.27646947470486</v>
+        <v>12.2917228306561</v>
       </c>
       <c r="E39">
-        <v>-7.460669749889754</v>
+        <v>-7.326214674494678</v>
       </c>
       <c r="F39">
-        <v>4.974837789617792</v>
+        <v>5.109292865012868</v>
       </c>
       <c r="G39">
         <v>1.29</v>
@@ -5836,28 +5836,28 @@
         <v>3.008</v>
       </c>
       <c r="M39">
-        <v>0.2576965975022016</v>
+        <v>0.2646613704076665</v>
       </c>
       <c r="N39">
-        <v>2.750303402497798</v>
+        <v>2.743338629592333</v>
       </c>
       <c r="O39">
-        <v>0.8250910207493395</v>
+        <v>0.8230015888777</v>
       </c>
       <c r="P39">
-        <v>1.925212381748459</v>
+        <v>1.920337040714633</v>
       </c>
       <c r="Q39">
-        <v>2.541212381748459</v>
+        <v>2.536337040714634</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1160099533868721</v>
+        <v>0.1169016215782217</v>
       </c>
       <c r="T39">
-        <v>1.621476983530533</v>
+        <v>1.642069782406969</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>11.67264150615843</v>
+        <v>11.36546672968057</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5882,22 +5882,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08625780537849746</v>
+        <v>0.08601314012326554</v>
       </c>
       <c r="C40">
-        <v>8.472429965643233</v>
+        <v>8.353266197551946</v>
       </c>
       <c r="D40">
-        <v>12.2917228306561</v>
+        <v>12.30701413795989</v>
       </c>
       <c r="E40">
-        <v>-7.326214674494678</v>
+        <v>-7.191759599099603</v>
       </c>
       <c r="F40">
-        <v>5.109292865012868</v>
+        <v>5.243747940407943</v>
       </c>
       <c r="G40">
         <v>1.29</v>
@@ -5918,28 +5918,28 @@
         <v>3.008</v>
       </c>
       <c r="M40">
-        <v>0.2646613704076665</v>
+        <v>0.2716261433131314</v>
       </c>
       <c r="N40">
-        <v>2.743338629592333</v>
+        <v>2.736373856686868</v>
       </c>
       <c r="O40">
-        <v>0.8230015888777</v>
+        <v>0.8209121570060606</v>
       </c>
       <c r="P40">
-        <v>1.920337040714633</v>
+        <v>1.915461699680808</v>
       </c>
       <c r="Q40">
-        <v>2.536337040714634</v>
+        <v>2.531461699680808</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1169016215782217</v>
+        <v>0.1178225247922386</v>
       </c>
       <c r="T40">
-        <v>1.642069782406969</v>
+        <v>1.663337755017058</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>11.36546672968057</v>
+        <v>11.07404450584261</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5964,22 +5964,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08601314012326554</v>
+        <v>0.08576847486803361</v>
       </c>
       <c r="C41">
-        <v>8.353266197551946</v>
+        <v>8.234140522627813</v>
       </c>
       <c r="D41">
-        <v>12.30701413795989</v>
+        <v>12.32234353843083</v>
       </c>
       <c r="E41">
-        <v>-7.191759599099603</v>
+        <v>-7.057304523704527</v>
       </c>
       <c r="F41">
-        <v>5.243747940407943</v>
+        <v>5.378203015803019</v>
       </c>
       <c r="G41">
         <v>1.29</v>
@@ -6000,28 +6000,28 @@
         <v>3.008</v>
       </c>
       <c r="M41">
-        <v>0.2716261433131314</v>
+        <v>0.2785909162185963</v>
       </c>
       <c r="N41">
-        <v>2.736373856686868</v>
+        <v>2.729409083781404</v>
       </c>
       <c r="O41">
-        <v>0.8209121570060606</v>
+        <v>0.818822725134421</v>
       </c>
       <c r="P41">
-        <v>1.915461699680808</v>
+        <v>1.910586358646983</v>
       </c>
       <c r="Q41">
-        <v>2.531461699680808</v>
+        <v>2.526586358646983</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1178225247922386</v>
+        <v>0.118774124780056</v>
       </c>
       <c r="T41">
-        <v>1.663337755017058</v>
+        <v>1.685314660047483</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.07404450584261</v>
+        <v>10.79719339319654</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -6046,22 +6046,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08576847486803361</v>
+        <v>0.08552380961280168</v>
       </c>
       <c r="C42">
-        <v>8.234140522627813</v>
+        <v>8.115053083392898</v>
       </c>
       <c r="D42">
-        <v>12.32234353843083</v>
+        <v>12.33771117459099</v>
       </c>
       <c r="E42">
-        <v>-7.057304523704527</v>
+        <v>-6.922849448309451</v>
       </c>
       <c r="F42">
-        <v>5.378203015803019</v>
+        <v>5.512658091198094</v>
       </c>
       <c r="G42">
         <v>1.29</v>
@@ -6082,28 +6082,28 @@
         <v>3.008</v>
       </c>
       <c r="M42">
-        <v>0.2785909162185963</v>
+        <v>0.2855556891240613</v>
       </c>
       <c r="N42">
-        <v>2.729409083781404</v>
+        <v>2.722444310875939</v>
       </c>
       <c r="O42">
-        <v>0.818822725134421</v>
+        <v>0.8167332932627815</v>
       </c>
       <c r="P42">
-        <v>1.910586358646983</v>
+        <v>1.905711017613157</v>
       </c>
       <c r="Q42">
-        <v>2.526586358646983</v>
+        <v>2.521711017613157</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.118774124780056</v>
+        <v>0.1197579823945791</v>
       </c>
       <c r="T42">
-        <v>1.685314660047483</v>
+        <v>1.708036544909449</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.79719339319654</v>
+        <v>10.53384721287468</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -6128,22 +6128,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08552380961280168</v>
+        <v>0.08527914435756974</v>
       </c>
       <c r="C43">
-        <v>8.115053083392898</v>
+        <v>7.996004023081134</v>
       </c>
       <c r="D43">
-        <v>12.33771117459099</v>
+        <v>12.3531171896743</v>
       </c>
       <c r="E43">
-        <v>-6.922849448309451</v>
+        <v>-6.788394372914376</v>
       </c>
       <c r="F43">
-        <v>5.512658091198094</v>
+        <v>5.64711316659317</v>
       </c>
       <c r="G43">
         <v>1.29</v>
@@ -6164,28 +6164,28 @@
         <v>3.008</v>
       </c>
       <c r="M43">
-        <v>0.2855556891240613</v>
+        <v>0.2925204620295262</v>
       </c>
       <c r="N43">
-        <v>2.722444310875939</v>
+        <v>2.715479537970474</v>
       </c>
       <c r="O43">
-        <v>0.8167332932627815</v>
+        <v>0.8146438613911421</v>
       </c>
       <c r="P43">
-        <v>1.905711017613157</v>
+        <v>1.900835676579332</v>
       </c>
       <c r="Q43">
-        <v>2.521711017613157</v>
+        <v>2.516835676579332</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1197579823945791</v>
+        <v>0.1207757661337409</v>
       </c>
       <c r="T43">
-        <v>1.708036544909449</v>
+        <v>1.731541943042516</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -6202,7 +6202,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>10.53384721287468</v>
+        <v>10.28304132685385</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -6210,22 +6210,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08527914435756975</v>
+        <v>0.08503447910233783</v>
       </c>
       <c r="C44">
-        <v>7.996004023081131</v>
+        <v>7.876993485642751</v>
       </c>
       <c r="D44">
-        <v>12.3531171896743</v>
+        <v>12.368561727631</v>
       </c>
       <c r="E44">
-        <v>-6.788394372914377</v>
+        <v>-6.653939297519301</v>
       </c>
       <c r="F44">
-        <v>5.647113166593169</v>
+        <v>5.781568241988245</v>
       </c>
       <c r="G44">
         <v>1.29</v>
@@ -6246,28 +6246,28 @@
         <v>3.008</v>
       </c>
       <c r="M44">
-        <v>0.2925204620295261</v>
+        <v>0.2994852349349911</v>
       </c>
       <c r="N44">
-        <v>2.715479537970474</v>
+        <v>2.708514765065009</v>
       </c>
       <c r="O44">
-        <v>0.8146438613911421</v>
+        <v>0.8125544295195026</v>
       </c>
       <c r="P44">
-        <v>1.900835676579332</v>
+        <v>1.895960335545506</v>
       </c>
       <c r="Q44">
-        <v>2.516835676579332</v>
+        <v>2.511960335545506</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1207757661337409</v>
+        <v>0.1218292615830488</v>
       </c>
       <c r="T44">
-        <v>1.731541943042516</v>
+        <v>1.75587209198727</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>10.28304132685385</v>
+        <v>10.0439008308805</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -6292,22 +6292,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08503447910233783</v>
+        <v>0.08478981384710588</v>
       </c>
       <c r="C45">
-        <v>7.876993485642751</v>
+        <v>7.7580216157488</v>
       </c>
       <c r="D45">
-        <v>12.368561727631</v>
+        <v>12.38404493313212</v>
       </c>
       <c r="E45">
-        <v>-6.653939297519301</v>
+        <v>-6.519484222124226</v>
       </c>
       <c r="F45">
-        <v>5.781568241988245</v>
+        <v>5.91602331738332</v>
       </c>
       <c r="G45">
         <v>1.29</v>
@@ -6328,28 +6328,28 @@
         <v>3.008</v>
       </c>
       <c r="M45">
-        <v>0.2994852349349911</v>
+        <v>0.306450007840456</v>
       </c>
       <c r="N45">
-        <v>2.708514765065009</v>
+        <v>2.701549992159544</v>
       </c>
       <c r="O45">
-        <v>0.8125544295195026</v>
+        <v>0.8104649976478632</v>
       </c>
       <c r="P45">
-        <v>1.895960335545506</v>
+        <v>1.891084994511681</v>
       </c>
       <c r="Q45">
-        <v>2.511960335545506</v>
+        <v>2.507084994511681</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1218292615830488</v>
+        <v>0.1229203818698319</v>
       </c>
       <c r="T45">
-        <v>1.75587209198727</v>
+        <v>1.781071174822908</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.0439008308805</v>
+        <v>9.815630357451402</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -6374,22 +6374,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08478981384710588</v>
+        <v>0.08508064859187395</v>
       </c>
       <c r="C46">
-        <v>7.7580216157488</v>
+        <v>7.605165922064642</v>
       </c>
       <c r="D46">
-        <v>12.38404493313212</v>
+        <v>12.36564431484304</v>
       </c>
       <c r="E46">
-        <v>-6.519484222124226</v>
+        <v>-6.38502914672915</v>
       </c>
       <c r="F46">
-        <v>5.91602331738332</v>
+        <v>6.050478392778396</v>
       </c>
       <c r="G46">
         <v>1.29</v>
@@ -6410,45 +6410,45 @@
         <v>3.008</v>
       </c>
       <c r="M46">
-        <v>0.306450007840456</v>
+        <v>0.3237005940136441</v>
       </c>
       <c r="N46">
-        <v>2.701549992159544</v>
+        <v>2.684299405986356</v>
       </c>
       <c r="O46">
-        <v>0.8104649976478632</v>
+        <v>0.8052898217959067</v>
       </c>
       <c r="P46">
-        <v>1.891084994511681</v>
+        <v>1.879009584190449</v>
       </c>
       <c r="Q46">
-        <v>2.507084994511681</v>
+        <v>2.495009584190449</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1229203818698319</v>
+        <v>0.1240511792579526</v>
       </c>
       <c r="T46">
-        <v>1.781071174822908</v>
+        <v>1.807186587943479</v>
       </c>
       <c r="U46">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>9.815630357451402</v>
+        <v>9.292537782223567</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -6456,22 +6456,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08508064859187395</v>
+        <v>0.084847883336642</v>
       </c>
       <c r="C47">
-        <v>7.605165922064642</v>
+        <v>7.485433133252223</v>
       </c>
       <c r="D47">
-        <v>12.36564431484304</v>
+        <v>12.38036660142569</v>
       </c>
       <c r="E47">
-        <v>-6.38502914672915</v>
+        <v>-6.250574071334074</v>
       </c>
       <c r="F47">
-        <v>6.050478392778396</v>
+        <v>6.184933468173472</v>
       </c>
       <c r="G47">
         <v>1.29</v>
@@ -6492,28 +6492,28 @@
         <v>3.008</v>
       </c>
       <c r="M47">
-        <v>0.3237005940136441</v>
+        <v>0.3308939405472807</v>
       </c>
       <c r="N47">
-        <v>2.684299405986356</v>
+        <v>2.677106059452719</v>
       </c>
       <c r="O47">
-        <v>0.8052898217959067</v>
+        <v>0.8031318178358158</v>
       </c>
       <c r="P47">
-        <v>1.879009584190449</v>
+        <v>1.873974241616904</v>
       </c>
       <c r="Q47">
-        <v>2.495009584190449</v>
+        <v>2.489974241616904</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1240511792579526</v>
+        <v>0.1252238580308185</v>
       </c>
       <c r="T47">
-        <v>1.807186587943479</v>
+        <v>1.834269238587033</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>9.292537782223567</v>
+        <v>9.090526091305662</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -6538,22 +6538,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.084847883336642</v>
+        <v>0.08461511808141009</v>
       </c>
       <c r="C48">
-        <v>7.485433133252223</v>
+        <v>7.365735442341276</v>
       </c>
       <c r="D48">
-        <v>12.38036660142569</v>
+        <v>12.39512398590982</v>
       </c>
       <c r="E48">
-        <v>-6.250574071334074</v>
+        <v>-6.116118995938999</v>
       </c>
       <c r="F48">
-        <v>6.184933468173472</v>
+        <v>6.319388543568547</v>
       </c>
       <c r="G48">
         <v>1.29</v>
@@ -6574,28 +6574,28 @@
         <v>3.008</v>
       </c>
       <c r="M48">
-        <v>0.3308939405472807</v>
+        <v>0.3380872870809172</v>
       </c>
       <c r="N48">
-        <v>2.677106059452719</v>
+        <v>2.669912712919083</v>
       </c>
       <c r="O48">
-        <v>0.8031318178358158</v>
+        <v>0.8009738138757249</v>
       </c>
       <c r="P48">
-        <v>1.873974241616904</v>
+        <v>1.868938899043358</v>
       </c>
       <c r="Q48">
-        <v>2.489974241616904</v>
+        <v>2.484938899043358</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1252238580308185</v>
+        <v>0.1264407888328492</v>
       </c>
       <c r="T48">
-        <v>1.834269238587033</v>
+        <v>1.862373876047326</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>9.090526091305662</v>
+        <v>8.89711064255448</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -6620,22 +6620,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08461511808141009</v>
+        <v>0.08438235282617815</v>
       </c>
       <c r="C49">
-        <v>7.365735442341276</v>
+        <v>7.246072974991575</v>
       </c>
       <c r="D49">
-        <v>12.39512398590982</v>
+        <v>12.4099165939552</v>
       </c>
       <c r="E49">
-        <v>-6.116118995938999</v>
+        <v>-5.981663920543923</v>
       </c>
       <c r="F49">
-        <v>6.319388543568547</v>
+        <v>6.453843618963623</v>
       </c>
       <c r="G49">
         <v>1.29</v>
@@ -6656,28 +6656,28 @@
         <v>3.008</v>
       </c>
       <c r="M49">
-        <v>0.3380872870809172</v>
+        <v>0.3452806336145538</v>
       </c>
       <c r="N49">
-        <v>2.669912712919083</v>
+        <v>2.662719366385446</v>
       </c>
       <c r="O49">
-        <v>0.8009738138757249</v>
+        <v>0.7988158099156338</v>
       </c>
       <c r="P49">
-        <v>1.868938899043358</v>
+        <v>1.863903556469812</v>
       </c>
       <c r="Q49">
-        <v>2.484938899043358</v>
+        <v>2.479903556469812</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1264407888328492</v>
+        <v>0.1277045246657272</v>
       </c>
       <c r="T49">
-        <v>1.862373876047326</v>
+        <v>1.891559461102245</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -6694,7 +6694,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.89711064255448</v>
+        <v>8.711754170834592</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -6702,22 +6702,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08438235282617815</v>
+        <v>0.0841495875709462</v>
       </c>
       <c r="C50">
-        <v>7.246072974991576</v>
+        <v>7.126445857463482</v>
       </c>
       <c r="D50">
-        <v>12.4099165939552</v>
+        <v>12.42474455182218</v>
       </c>
       <c r="E50">
-        <v>-5.981663920543924</v>
+        <v>-5.847208845148849</v>
       </c>
       <c r="F50">
-        <v>6.453843618963622</v>
+        <v>6.588298694358697</v>
       </c>
       <c r="G50">
         <v>1.29</v>
@@ -6738,28 +6738,28 @@
         <v>3.008</v>
       </c>
       <c r="M50">
-        <v>0.3452806336145537</v>
+        <v>0.3524739801481903</v>
       </c>
       <c r="N50">
-        <v>2.662719366385446</v>
+        <v>2.65552601985181</v>
       </c>
       <c r="O50">
-        <v>0.7988158099156339</v>
+        <v>0.7966578059555428</v>
       </c>
       <c r="P50">
-        <v>1.863903556469813</v>
+        <v>1.858868213896267</v>
       </c>
       <c r="Q50">
-        <v>2.479903556469813</v>
+        <v>2.474868213896267</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1277045246657272</v>
+        <v>0.1290178187665612</v>
       </c>
       <c r="T50">
-        <v>1.891559461102245</v>
+        <v>1.921889578904416</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -6776,7 +6776,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.711754170834595</v>
+        <v>8.533963269388991</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -6784,22 +6784,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0841495875709462</v>
+        <v>0.08391682231571429</v>
       </c>
       <c r="C51">
-        <v>7.126445857463482</v>
+        <v>7.006854216621505</v>
       </c>
       <c r="D51">
-        <v>12.42474455182218</v>
+        <v>12.43960798637528</v>
       </c>
       <c r="E51">
-        <v>-5.847208845148849</v>
+        <v>-5.712753769753773</v>
       </c>
       <c r="F51">
-        <v>6.588298694358697</v>
+        <v>6.722753769753773</v>
       </c>
       <c r="G51">
         <v>1.29</v>
@@ -6820,28 +6820,28 @@
         <v>3.008</v>
       </c>
       <c r="M51">
-        <v>0.3524739801481903</v>
+        <v>0.3596673266818268</v>
       </c>
       <c r="N51">
-        <v>2.65552601985181</v>
+        <v>2.648332673318173</v>
       </c>
       <c r="O51">
-        <v>0.7966578059555428</v>
+        <v>0.7944998019954519</v>
       </c>
       <c r="P51">
-        <v>1.858868213896267</v>
+        <v>1.853832871322721</v>
       </c>
       <c r="Q51">
-        <v>2.474868213896267</v>
+        <v>2.469832871322721</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1290178187665612</v>
+        <v>0.1303836446314286</v>
       </c>
       <c r="T51">
-        <v>1.921889578904416</v>
+        <v>1.953432901418674</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.533963269388991</v>
+        <v>8.36328400400121</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6866,22 +6866,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08391682231571429</v>
+        <v>0.08368405706048235</v>
       </c>
       <c r="C52">
-        <v>7.006854216621505</v>
+        <v>6.887298179937963</v>
       </c>
       <c r="D52">
-        <v>12.43960798637528</v>
+        <v>12.45450702508681</v>
       </c>
       <c r="E52">
-        <v>-5.712753769753773</v>
+        <v>-5.578298694358697</v>
       </c>
       <c r="F52">
-        <v>6.722753769753773</v>
+        <v>6.857208845148849</v>
       </c>
       <c r="G52">
         <v>1.29</v>
@@ -6902,28 +6902,28 @@
         <v>3.008</v>
       </c>
       <c r="M52">
-        <v>0.3596673266818268</v>
+        <v>0.3668606732154634</v>
       </c>
       <c r="N52">
-        <v>2.648332673318173</v>
+        <v>2.641139326784537</v>
       </c>
       <c r="O52">
-        <v>0.7944998019954519</v>
+        <v>0.792341798035361</v>
       </c>
       <c r="P52">
-        <v>1.853832871322721</v>
+        <v>1.848797528749176</v>
       </c>
       <c r="Q52">
-        <v>2.469832871322721</v>
+        <v>2.464797528749176</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1303836446314286</v>
+        <v>0.1318052184907803</v>
       </c>
       <c r="T52">
-        <v>1.953432901418674</v>
+        <v>1.986263706484534</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.36328400400121</v>
+        <v>8.199298043138441</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6948,22 +6948,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08368405706048235</v>
+        <v>0.08345129180525043</v>
       </c>
       <c r="C53">
-        <v>6.887298179937963</v>
+        <v>6.767777875496596</v>
       </c>
       <c r="D53">
-        <v>12.45450702508681</v>
+        <v>12.46944179604052</v>
       </c>
       <c r="E53">
-        <v>-5.578298694358697</v>
+        <v>-5.443843618963622</v>
       </c>
       <c r="F53">
-        <v>6.857208845148849</v>
+        <v>6.991663920543924</v>
       </c>
       <c r="G53">
         <v>1.29</v>
@@ -6984,28 +6984,28 @@
         <v>3.008</v>
       </c>
       <c r="M53">
-        <v>0.3668606732154634</v>
+        <v>0.3740540197490999</v>
       </c>
       <c r="N53">
-        <v>2.641139326784537</v>
+        <v>2.6339459802509</v>
       </c>
       <c r="O53">
-        <v>0.792341798035361</v>
+        <v>0.7901837940752701</v>
       </c>
       <c r="P53">
-        <v>1.848797528749176</v>
+        <v>1.84376218617563</v>
       </c>
       <c r="Q53">
-        <v>2.464797528749176</v>
+        <v>2.45976218617563</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1318052184907803</v>
+        <v>0.1332860245942717</v>
       </c>
       <c r="T53">
-        <v>1.986263706484534</v>
+        <v>2.020462461761471</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.199298043138441</v>
+        <v>8.041619234616547</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -7030,22 +7030,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08345129180525043</v>
+        <v>0.08321852655001849</v>
       </c>
       <c r="C54">
-        <v>6.767777875496596</v>
+        <v>6.648293431996247</v>
       </c>
       <c r="D54">
-        <v>12.46944179604052</v>
+        <v>12.48441242793525</v>
       </c>
       <c r="E54">
-        <v>-5.443843618963622</v>
+        <v>-5.309388543568546</v>
       </c>
       <c r="F54">
-        <v>6.991663920543924</v>
+        <v>7.126118995939</v>
       </c>
       <c r="G54">
         <v>1.29</v>
@@ -7066,28 +7066,28 @@
         <v>3.008</v>
       </c>
       <c r="M54">
-        <v>0.3740540197490999</v>
+        <v>0.3812473662827365</v>
       </c>
       <c r="N54">
-        <v>2.6339459802509</v>
+        <v>2.626752633717263</v>
       </c>
       <c r="O54">
-        <v>0.7901837940752701</v>
+        <v>0.7880257901151789</v>
       </c>
       <c r="P54">
-        <v>1.84376218617563</v>
+        <v>1.838726843602084</v>
       </c>
       <c r="Q54">
-        <v>2.45976218617563</v>
+        <v>2.454726843602085</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1332860245942717</v>
+        <v>0.1348298437234436</v>
       </c>
       <c r="T54">
-        <v>2.020462461761471</v>
+        <v>2.056116483220406</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -7104,7 +7104,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.041619234616547</v>
+        <v>7.889890569812462</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -7112,22 +7112,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08321852655001849</v>
+        <v>0.08298576129478655</v>
       </c>
       <c r="C55">
-        <v>6.648293431996247</v>
+        <v>6.528844978754554</v>
       </c>
       <c r="D55">
-        <v>12.48441242793525</v>
+        <v>12.49941905008863</v>
       </c>
       <c r="E55">
-        <v>-5.309388543568546</v>
+        <v>-5.174933468173471</v>
       </c>
       <c r="F55">
-        <v>7.126118995939</v>
+        <v>7.260574071334075</v>
       </c>
       <c r="G55">
         <v>1.29</v>
@@ -7148,28 +7148,28 @@
         <v>3.008</v>
       </c>
       <c r="M55">
-        <v>0.3812473662827365</v>
+        <v>0.388440712816373</v>
       </c>
       <c r="N55">
-        <v>2.626752633717263</v>
+        <v>2.619559287183627</v>
       </c>
       <c r="O55">
-        <v>0.7880257901151789</v>
+        <v>0.785867786155088</v>
       </c>
       <c r="P55">
-        <v>1.838726843602084</v>
+        <v>1.833691501028539</v>
       </c>
       <c r="Q55">
-        <v>2.454726843602085</v>
+        <v>2.449691501028539</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1348298437234436</v>
+        <v>0.136440785423449</v>
       </c>
       <c r="T55">
-        <v>2.056116483220406</v>
+        <v>2.093320679525382</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.889890569812462</v>
+        <v>7.743781485186305</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -7194,22 +7194,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08298576129478655</v>
+        <v>0.08306099603955461</v>
       </c>
       <c r="C56">
-        <v>6.528844978754554</v>
+        <v>6.389535495449511</v>
       </c>
       <c r="D56">
-        <v>12.49941905008863</v>
+        <v>12.49456464217866</v>
       </c>
       <c r="E56">
-        <v>-5.174933468173471</v>
+        <v>-5.040478392778395</v>
       </c>
       <c r="F56">
-        <v>7.260574071334075</v>
+        <v>7.395029146729151</v>
       </c>
       <c r="G56">
         <v>1.29</v>
@@ -7230,45 +7230,45 @@
         <v>3.008</v>
       </c>
       <c r="M56">
-        <v>0.388440712816373</v>
+        <v>0.4015500826673929</v>
       </c>
       <c r="N56">
-        <v>2.619559287183627</v>
+        <v>2.606449917332607</v>
       </c>
       <c r="O56">
-        <v>0.785867786155088</v>
+        <v>0.7819349751997822</v>
       </c>
       <c r="P56">
-        <v>1.833691501028539</v>
+        <v>1.824514942132825</v>
       </c>
       <c r="Q56">
-        <v>2.449691501028539</v>
+        <v>2.440514942132825</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.136440785423449</v>
+        <v>0.1381233245323436</v>
       </c>
       <c r="T56">
-        <v>2.093320679525382</v>
+        <v>2.132178395666134</v>
       </c>
       <c r="U56">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V56">
         <v>0.3</v>
       </c>
       <c r="W56">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y56">
-        <v>7.743781485186305</v>
+        <v>7.490970939461991</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -7276,22 +7276,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08306099603955461</v>
+        <v>0.08283383078432269</v>
       </c>
       <c r="C57">
-        <v>6.389535495449511</v>
+        <v>6.269749423070276</v>
       </c>
       <c r="D57">
-        <v>12.49456464217866</v>
+        <v>12.5092336451945</v>
       </c>
       <c r="E57">
-        <v>-5.040478392778395</v>
+        <v>-4.90602331738332</v>
       </c>
       <c r="F57">
-        <v>7.395029146729151</v>
+        <v>7.529484222124226</v>
       </c>
       <c r="G57">
         <v>1.29</v>
@@ -7312,28 +7312,28 @@
         <v>3.008</v>
       </c>
       <c r="M57">
-        <v>0.4015500826673929</v>
+        <v>0.4088509932613454</v>
       </c>
       <c r="N57">
-        <v>2.606449917332607</v>
+        <v>2.599149006738655</v>
       </c>
       <c r="O57">
-        <v>0.7819349751997822</v>
+        <v>0.7797447020215964</v>
       </c>
       <c r="P57">
-        <v>1.824514942132825</v>
+        <v>1.819404304717058</v>
       </c>
       <c r="Q57">
-        <v>2.440514942132825</v>
+        <v>2.435404304717058</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1381233245323436</v>
+        <v>0.1398823426916425</v>
       </c>
       <c r="T57">
-        <v>2.132178395666134</v>
+        <v>2.172802371631466</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.490970939461991</v>
+        <v>7.357203601257313</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -7358,22 +7358,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08283383078432269</v>
+        <v>0.08260666552909074</v>
       </c>
       <c r="C58">
-        <v>6.269749423070276</v>
+        <v>6.149997834897598</v>
       </c>
       <c r="D58">
-        <v>12.5092336451945</v>
+        <v>12.5239371324169</v>
       </c>
       <c r="E58">
-        <v>-4.90602331738332</v>
+        <v>-4.771568241988244</v>
       </c>
       <c r="F58">
-        <v>7.529484222124226</v>
+        <v>7.663939297519302</v>
       </c>
       <c r="G58">
         <v>1.29</v>
@@ -7394,28 +7394,28 @@
         <v>3.008</v>
       </c>
       <c r="M58">
-        <v>0.4088509932613454</v>
+        <v>0.4161519038552981</v>
       </c>
       <c r="N58">
-        <v>2.599149006738655</v>
+        <v>2.591848096144702</v>
       </c>
       <c r="O58">
-        <v>0.7797447020215964</v>
+        <v>0.7775544288434105</v>
       </c>
       <c r="P58">
-        <v>1.819404304717058</v>
+        <v>1.814293667301291</v>
       </c>
       <c r="Q58">
-        <v>2.435404304717058</v>
+        <v>2.430293667301291</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1398823426916425</v>
+        <v>0.1417231756490483</v>
       </c>
       <c r="T58">
-        <v>2.172802371631466</v>
+        <v>2.215315834850999</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.357203601257313</v>
+        <v>7.228129853866832</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -7440,22 +7440,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08260666552909074</v>
+        <v>0.08237950027385882</v>
       </c>
       <c r="C59">
-        <v>6.149997834897598</v>
+        <v>6.030280852673882</v>
       </c>
       <c r="D59">
-        <v>12.5239371324169</v>
+        <v>12.53867522558826</v>
       </c>
       <c r="E59">
-        <v>-4.771568241988244</v>
+        <v>-4.637113166593168</v>
       </c>
       <c r="F59">
-        <v>7.663939297519302</v>
+        <v>7.798394372914378</v>
       </c>
       <c r="G59">
         <v>1.29</v>
@@ -7476,28 +7476,28 @@
         <v>3.008</v>
       </c>
       <c r="M59">
-        <v>0.4161519038552981</v>
+        <v>0.4234528144492507</v>
       </c>
       <c r="N59">
-        <v>2.591848096144702</v>
+        <v>2.584547185550749</v>
       </c>
       <c r="O59">
-        <v>0.7775544288434105</v>
+        <v>0.7753641556652248</v>
       </c>
       <c r="P59">
-        <v>1.814293667301291</v>
+        <v>1.809183029885524</v>
       </c>
       <c r="Q59">
-        <v>2.430293667301291</v>
+        <v>2.425183029885524</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1417231756490483</v>
+        <v>0.1436516673187115</v>
       </c>
       <c r="T59">
-        <v>2.215315834850999</v>
+        <v>2.259853748700035</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>7.228129853866832</v>
+        <v>7.103506925351887</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -7522,22 +7522,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08237950027385882</v>
+        <v>0.08215233501862688</v>
       </c>
       <c r="C60">
-        <v>6.030280852673884</v>
+        <v>5.910598598715286</v>
       </c>
       <c r="D60">
-        <v>12.53867522558826</v>
+        <v>12.55344804702474</v>
       </c>
       <c r="E60">
-        <v>-4.63711316659317</v>
+        <v>-4.502658091198095</v>
       </c>
       <c r="F60">
-        <v>7.798394372914376</v>
+        <v>7.932849448309451</v>
       </c>
       <c r="G60">
         <v>1.29</v>
@@ -7558,28 +7558,28 @@
         <v>3.008</v>
       </c>
       <c r="M60">
-        <v>0.4234528144492506</v>
+        <v>0.4307537250432032</v>
       </c>
       <c r="N60">
-        <v>2.58454718555075</v>
+        <v>2.577246274956797</v>
       </c>
       <c r="O60">
-        <v>0.7753641556652249</v>
+        <v>0.773173882487039</v>
       </c>
       <c r="P60">
-        <v>1.809183029885525</v>
+        <v>1.804072392469758</v>
       </c>
       <c r="Q60">
-        <v>2.425183029885525</v>
+        <v>2.420072392469758</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1436516673187115</v>
+        <v>0.1456742317527485</v>
       </c>
       <c r="T60">
-        <v>2.259853748700034</v>
+        <v>2.306564243712436</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -7596,7 +7596,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>7.10350692535189</v>
+        <v>6.983108502888297</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -7604,22 +7604,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08215233501862688</v>
+        <v>0.08192516976339495</v>
       </c>
       <c r="C61">
-        <v>5.910598598715286</v>
+        <v>5.790951195915083</v>
       </c>
       <c r="D61">
-        <v>12.55344804702474</v>
+        <v>12.56825571961961</v>
       </c>
       <c r="E61">
-        <v>-4.502658091198095</v>
+        <v>-4.368203015803019</v>
       </c>
       <c r="F61">
-        <v>7.932849448309451</v>
+        <v>8.067304523704527</v>
       </c>
       <c r="G61">
         <v>1.29</v>
@@ -7640,28 +7640,28 @@
         <v>3.008</v>
       </c>
       <c r="M61">
-        <v>0.4307537250432032</v>
+        <v>0.4380546356371558</v>
       </c>
       <c r="N61">
-        <v>2.577246274956797</v>
+        <v>2.569945364362844</v>
       </c>
       <c r="O61">
-        <v>0.773173882487039</v>
+        <v>0.7709836093088532</v>
       </c>
       <c r="P61">
-        <v>1.804072392469758</v>
+        <v>1.798961755053991</v>
       </c>
       <c r="Q61">
-        <v>2.420072392469758</v>
+        <v>2.414961755053991</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1456742317527485</v>
+        <v>0.1477979244084874</v>
       </c>
       <c r="T61">
-        <v>2.306564243712436</v>
+        <v>2.355610263475459</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.983108502888297</v>
+        <v>6.866723361173492</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -7686,22 +7686,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08192516976339495</v>
+        <v>0.08169800450816303</v>
       </c>
       <c r="C62">
-        <v>5.790951195915083</v>
+        <v>5.671338767747077</v>
       </c>
       <c r="D62">
-        <v>12.56825571961961</v>
+        <v>12.58309836684668</v>
       </c>
       <c r="E62">
-        <v>-4.368203015803019</v>
+        <v>-4.233747940407943</v>
       </c>
       <c r="F62">
-        <v>8.067304523704527</v>
+        <v>8.201759599099603</v>
       </c>
       <c r="G62">
         <v>1.29</v>
@@ -7722,28 +7722,28 @@
         <v>3.008</v>
       </c>
       <c r="M62">
-        <v>0.4380546356371558</v>
+        <v>0.4453555462311085</v>
       </c>
       <c r="N62">
-        <v>2.569945364362844</v>
+        <v>2.562644453768891</v>
       </c>
       <c r="O62">
-        <v>0.7709836093088532</v>
+        <v>0.7687933361306675</v>
       </c>
       <c r="P62">
-        <v>1.798961755053991</v>
+        <v>1.793851117638224</v>
       </c>
       <c r="Q62">
-        <v>2.414961755053991</v>
+        <v>2.409851117638224</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1477979244084874</v>
+        <v>0.1500305243799052</v>
       </c>
       <c r="T62">
-        <v>2.355610263475459</v>
+        <v>2.40717146373915</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -7760,7 +7760,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.866723361173492</v>
+        <v>6.754154125744417</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -7768,22 +7768,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08169800450816303</v>
+        <v>0.08147083925293108</v>
       </c>
       <c r="C63">
-        <v>5.671338767747077</v>
+        <v>5.551761438269038</v>
       </c>
       <c r="D63">
-        <v>12.58309836684668</v>
+        <v>12.59797611276372</v>
       </c>
       <c r="E63">
-        <v>-4.233747940407943</v>
+        <v>-4.099292865012867</v>
       </c>
       <c r="F63">
-        <v>8.201759599099603</v>
+        <v>8.336214674494679</v>
       </c>
       <c r="G63">
         <v>1.29</v>
@@ -7804,28 +7804,28 @@
         <v>3.008</v>
       </c>
       <c r="M63">
-        <v>0.4453555462311085</v>
+        <v>0.4526564568250611</v>
       </c>
       <c r="N63">
-        <v>2.562644453768891</v>
+        <v>2.555343543174939</v>
       </c>
       <c r="O63">
-        <v>0.7687933361306675</v>
+        <v>0.7666030629524817</v>
       </c>
       <c r="P63">
-        <v>1.793851117638224</v>
+        <v>1.788740480222457</v>
       </c>
       <c r="Q63">
-        <v>2.409851117638224</v>
+        <v>2.404740480222457</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1500305243799052</v>
+        <v>0.1523806296129765</v>
       </c>
       <c r="T63">
-        <v>2.40717146373915</v>
+        <v>2.46144641138514</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -7842,7 +7842,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.754154125744417</v>
+        <v>6.645216155974347</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -7850,22 +7850,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08147083925293108</v>
+        <v>0.08124367399769916</v>
       </c>
       <c r="C64">
-        <v>5.551761438269038</v>
+        <v>5.432219332126143</v>
       </c>
       <c r="D64">
-        <v>12.59797611276372</v>
+        <v>12.6128890820159</v>
       </c>
       <c r="E64">
-        <v>-4.099292865012867</v>
+        <v>-3.964837789617793</v>
       </c>
       <c r="F64">
-        <v>8.336214674494679</v>
+        <v>8.470669749889753</v>
       </c>
       <c r="G64">
         <v>1.29</v>
@@ -7886,28 +7886,28 @@
         <v>3.008</v>
       </c>
       <c r="M64">
-        <v>0.4526564568250611</v>
+        <v>0.4599573674190136</v>
       </c>
       <c r="N64">
-        <v>2.555343543174939</v>
+        <v>2.548042632580986</v>
       </c>
       <c r="O64">
-        <v>0.7666030629524817</v>
+        <v>0.7644127897742959</v>
       </c>
       <c r="P64">
-        <v>1.788740480222457</v>
+        <v>1.783629842806691</v>
       </c>
       <c r="Q64">
-        <v>2.404740480222457</v>
+        <v>2.399629842806691</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1523806296129765</v>
+        <v>0.1548577675613491</v>
       </c>
       <c r="T64">
-        <v>2.46144641138514</v>
+        <v>2.518655139984967</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -7924,7 +7924,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.645216155974347</v>
+        <v>6.539736534450945</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7932,22 +7932,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08124367399769916</v>
+        <v>0.08101650874246721</v>
       </c>
       <c r="C65">
-        <v>5.432219332126143</v>
+        <v>5.312712574554482</v>
       </c>
       <c r="D65">
-        <v>12.6128890820159</v>
+        <v>12.62783739983931</v>
       </c>
       <c r="E65">
-        <v>-3.964837789617793</v>
+        <v>-3.830382714222717</v>
       </c>
       <c r="F65">
-        <v>8.470669749889753</v>
+        <v>8.605124825284829</v>
       </c>
       <c r="G65">
         <v>1.29</v>
@@ -7968,28 +7968,28 @@
         <v>3.008</v>
       </c>
       <c r="M65">
-        <v>0.4599573674190136</v>
+        <v>0.4672582780129662</v>
       </c>
       <c r="N65">
-        <v>2.548042632580986</v>
+        <v>2.540741721987034</v>
       </c>
       <c r="O65">
-        <v>0.7644127897742959</v>
+        <v>0.7622225165961102</v>
       </c>
       <c r="P65">
-        <v>1.783629842806691</v>
+        <v>1.778519205390924</v>
       </c>
       <c r="Q65">
-        <v>2.399629842806691</v>
+        <v>2.394519205390924</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1548577675613491</v>
+        <v>0.1574725242846312</v>
       </c>
       <c r="T65">
-        <v>2.518655139984967</v>
+        <v>2.579042131284785</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.539736534450945</v>
+        <v>6.437553151100149</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -8014,22 +8014,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08101650874246721</v>
+        <v>0.08078934348723529</v>
       </c>
       <c r="C66">
-        <v>5.312712574554482</v>
+        <v>5.193241291384536</v>
       </c>
       <c r="D66">
-        <v>12.62783739983931</v>
+        <v>12.64282119206444</v>
       </c>
       <c r="E66">
-        <v>-3.830382714222717</v>
+        <v>-3.695927638827641</v>
       </c>
       <c r="F66">
-        <v>8.605124825284829</v>
+        <v>8.739579900679905</v>
       </c>
       <c r="G66">
         <v>1.29</v>
@@ -8050,28 +8050,28 @@
         <v>3.008</v>
       </c>
       <c r="M66">
-        <v>0.4672582780129662</v>
+        <v>0.4745591886069189</v>
       </c>
       <c r="N66">
-        <v>2.540741721987034</v>
+        <v>2.533440811393081</v>
       </c>
       <c r="O66">
-        <v>0.7622225165961102</v>
+        <v>0.7600322434179244</v>
       </c>
       <c r="P66">
-        <v>1.778519205390924</v>
+        <v>1.773408567975157</v>
       </c>
       <c r="Q66">
-        <v>2.394519205390924</v>
+        <v>2.389408567975157</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1574725242846312</v>
+        <v>0.1602366956778151</v>
       </c>
       <c r="T66">
-        <v>2.579042131284785</v>
+        <v>2.642879807801735</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.437553151100149</v>
+        <v>6.338513871852454</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -8096,22 +8096,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08078934348723529</v>
+        <v>0.08056217823200336</v>
       </c>
       <c r="C67">
-        <v>5.193241291384536</v>
+        <v>5.073805609044737</v>
       </c>
       <c r="D67">
-        <v>12.64282119206444</v>
+        <v>12.65784058511972</v>
       </c>
       <c r="E67">
-        <v>-3.695927638827641</v>
+        <v>-3.561472563432565</v>
       </c>
       <c r="F67">
-        <v>8.739579900679905</v>
+        <v>8.874034976074981</v>
       </c>
       <c r="G67">
         <v>1.29</v>
@@ -8132,28 +8132,28 @@
         <v>3.008</v>
       </c>
       <c r="M67">
-        <v>0.4745591886069189</v>
+        <v>0.4818600992008715</v>
       </c>
       <c r="N67">
-        <v>2.533440811393081</v>
+        <v>2.526139900799128</v>
       </c>
       <c r="O67">
-        <v>0.7600322434179244</v>
+        <v>0.7578419702397384</v>
       </c>
       <c r="P67">
-        <v>1.773408567975157</v>
+        <v>1.76829793055939</v>
       </c>
       <c r="Q67">
-        <v>2.389408567975157</v>
+        <v>2.38429793055939</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1602366956778151</v>
+        <v>0.1631634653882452</v>
       </c>
       <c r="T67">
-        <v>2.642879807801735</v>
+        <v>2.710472641760859</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -8170,7 +8170,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.338513871852454</v>
+        <v>6.242475782884991</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -8178,22 +8178,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08056217823200336</v>
+        <v>0.08033501297677142</v>
       </c>
       <c r="C68">
-        <v>5.073805609044737</v>
+        <v>4.954405654564992</v>
       </c>
       <c r="D68">
-        <v>12.65784058511972</v>
+        <v>12.67289570603505</v>
       </c>
       <c r="E68">
-        <v>-3.561472563432565</v>
+        <v>-3.427017488037489</v>
       </c>
       <c r="F68">
-        <v>8.874034976074981</v>
+        <v>9.008490051470057</v>
       </c>
       <c r="G68">
         <v>1.29</v>
@@ -8214,28 +8214,28 @@
         <v>3.008</v>
       </c>
       <c r="M68">
-        <v>0.4818600992008715</v>
+        <v>0.4891610097948241</v>
       </c>
       <c r="N68">
-        <v>2.526139900799128</v>
+        <v>2.518838990205176</v>
       </c>
       <c r="O68">
-        <v>0.7578419702397384</v>
+        <v>0.7556516970615527</v>
       </c>
       <c r="P68">
-        <v>1.76829793055939</v>
+        <v>1.763187293143623</v>
       </c>
       <c r="Q68">
-        <v>2.38429793055939</v>
+        <v>2.379187293143623</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1631634653882452</v>
+        <v>0.1662676150811256</v>
       </c>
       <c r="T68">
-        <v>2.710472641760859</v>
+        <v>2.782162011111445</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -8252,7 +8252,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.242475782884991</v>
+        <v>6.149304502543425</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -8260,22 +8260,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08033501297677142</v>
+        <v>0.08058384772153949</v>
       </c>
       <c r="C69">
-        <v>4.954405654564992</v>
+        <v>4.803461205904183</v>
       </c>
       <c r="D69">
-        <v>12.67289570603505</v>
+        <v>12.65640633276931</v>
       </c>
       <c r="E69">
-        <v>-3.427017488037489</v>
+        <v>-3.292562412642415</v>
       </c>
       <c r="F69">
-        <v>9.008490051470057</v>
+        <v>9.142945126865131</v>
       </c>
       <c r="G69">
         <v>1.29</v>
@@ -8296,45 +8296,45 @@
         <v>3.008</v>
       </c>
       <c r="M69">
-        <v>0.4891610097948241</v>
+        <v>0.5056048655156418</v>
       </c>
       <c r="N69">
-        <v>2.518838990205176</v>
+        <v>2.502395134484358</v>
       </c>
       <c r="O69">
-        <v>0.7556516970615527</v>
+        <v>0.7507185403453075</v>
       </c>
       <c r="P69">
-        <v>1.763187293143623</v>
+        <v>1.751676594139051</v>
       </c>
       <c r="Q69">
-        <v>2.379187293143623</v>
+        <v>2.367676594139051</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1662676150811256</v>
+        <v>0.1695657741298109</v>
       </c>
       <c r="T69">
-        <v>2.782162011111445</v>
+        <v>2.858331966046442</v>
       </c>
       <c r="U69">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V69">
         <v>0.3</v>
       </c>
       <c r="W69">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>6.149304502543425</v>
+        <v>5.949309836906509</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -8342,22 +8342,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08058384772153949</v>
+        <v>0.08036368246630757</v>
       </c>
       <c r="C70">
-        <v>4.803461205904183</v>
+        <v>4.683593491330235</v>
       </c>
       <c r="D70">
-        <v>12.65640633276931</v>
+        <v>12.67099369359044</v>
       </c>
       <c r="E70">
-        <v>-3.292562412642415</v>
+        <v>-3.158107337247339</v>
       </c>
       <c r="F70">
-        <v>9.142945126865131</v>
+        <v>9.277400202260207</v>
       </c>
       <c r="G70">
         <v>1.29</v>
@@ -8378,28 +8378,28 @@
         <v>3.008</v>
       </c>
       <c r="M70">
-        <v>0.5056048655156418</v>
+        <v>0.5130402311849894</v>
       </c>
       <c r="N70">
-        <v>2.502395134484358</v>
+        <v>2.49495976881501</v>
       </c>
       <c r="O70">
-        <v>0.7507185403453075</v>
+        <v>0.7484879306445031</v>
       </c>
       <c r="P70">
-        <v>1.751676594139051</v>
+        <v>1.746471838170507</v>
       </c>
       <c r="Q70">
-        <v>2.367676594139051</v>
+        <v>2.362471838170507</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1695657741298109</v>
+        <v>0.1730767176332502</v>
       </c>
       <c r="T70">
-        <v>2.858331966046442</v>
+        <v>2.939416111622407</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -8416,7 +8416,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.949309836906509</v>
+        <v>5.863087955212212</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -8424,22 +8424,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08036368246630757</v>
+        <v>0.08014351721107563</v>
       </c>
       <c r="C71">
-        <v>4.683593491330235</v>
+        <v>4.563759441388912</v>
       </c>
       <c r="D71">
-        <v>12.67099369359044</v>
+        <v>12.6856147190442</v>
       </c>
       <c r="E71">
-        <v>-3.158107337247339</v>
+        <v>-3.023652261852263</v>
       </c>
       <c r="F71">
-        <v>9.277400202260207</v>
+        <v>9.411855277655283</v>
       </c>
       <c r="G71">
         <v>1.29</v>
@@ -8460,28 +8460,28 @@
         <v>3.008</v>
       </c>
       <c r="M71">
-        <v>0.5130402311849894</v>
+        <v>0.5204755968543372</v>
       </c>
       <c r="N71">
-        <v>2.49495976881501</v>
+        <v>2.487524403145663</v>
       </c>
       <c r="O71">
-        <v>0.7484879306445031</v>
+        <v>0.7462573209436988</v>
       </c>
       <c r="P71">
-        <v>1.746471838170507</v>
+        <v>1.741267082201964</v>
       </c>
       <c r="Q71">
-        <v>2.362471838170507</v>
+        <v>2.357267082201964</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1730767176332502</v>
+        <v>0.1768217240369188</v>
       </c>
       <c r="T71">
-        <v>2.939416111622407</v>
+        <v>3.025905866903436</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -8498,7 +8498,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.863087955212212</v>
+        <v>5.779329555852036</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -8506,22 +8506,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08014351721107563</v>
+        <v>0.07992335195584371</v>
       </c>
       <c r="C72">
-        <v>4.563759441388912</v>
+        <v>4.443959172751434</v>
       </c>
       <c r="D72">
-        <v>12.6856147190442</v>
+        <v>12.70026952580179</v>
       </c>
       <c r="E72">
-        <v>-3.023652261852263</v>
+        <v>-2.889197186457187</v>
       </c>
       <c r="F72">
-        <v>9.411855277655283</v>
+        <v>9.546310353050359</v>
       </c>
       <c r="G72">
         <v>1.29</v>
@@ -8542,28 +8542,28 @@
         <v>3.008</v>
       </c>
       <c r="M72">
-        <v>0.5204755968543372</v>
+        <v>0.5279109625236849</v>
       </c>
       <c r="N72">
-        <v>2.487524403145663</v>
+        <v>2.480089037476315</v>
       </c>
       <c r="O72">
-        <v>0.7462573209436988</v>
+        <v>0.7440267112428944</v>
       </c>
       <c r="P72">
-        <v>1.741267082201964</v>
+        <v>1.73606232623342</v>
       </c>
       <c r="Q72">
-        <v>2.357267082201964</v>
+        <v>2.35206232623342</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1768217240369188</v>
+        <v>0.1808250067442887</v>
       </c>
       <c r="T72">
-        <v>3.025905866903436</v>
+        <v>3.118360432893502</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.779329555852036</v>
+        <v>5.697930548023134</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -8588,22 +8588,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0799233519558437</v>
+        <v>0.07970318670061177</v>
       </c>
       <c r="C73">
-        <v>4.443959172751436</v>
+        <v>4.324192802628762</v>
       </c>
       <c r="D73">
-        <v>12.70026952580179</v>
+        <v>12.7149582310742</v>
       </c>
       <c r="E73">
-        <v>-2.889197186457189</v>
+        <v>-2.754742111062113</v>
       </c>
       <c r="F73">
-        <v>9.546310353050357</v>
+        <v>9.680765428445433</v>
       </c>
       <c r="G73">
         <v>1.29</v>
@@ -8624,28 +8624,28 @@
         <v>3.008</v>
       </c>
       <c r="M73">
-        <v>0.5279109625236847</v>
+        <v>0.5353463281930325</v>
       </c>
       <c r="N73">
-        <v>2.480089037476315</v>
+        <v>2.472653671806968</v>
       </c>
       <c r="O73">
-        <v>0.7440267112428945</v>
+        <v>0.7417961015420903</v>
       </c>
       <c r="P73">
-        <v>1.736062326233421</v>
+        <v>1.730857570264877</v>
       </c>
       <c r="Q73">
-        <v>2.352062326233421</v>
+        <v>2.346857570264878</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1808250067442886</v>
+        <v>0.1851142382164706</v>
       </c>
       <c r="T73">
-        <v>3.118360432893501</v>
+        <v>3.217418896454286</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.697930548023136</v>
+        <v>5.618792623745036</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -8670,22 +8670,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07970318670061177</v>
+        <v>0.07948302144537983</v>
       </c>
       <c r="C74">
-        <v>4.324192802628762</v>
+        <v>4.204460448774739</v>
       </c>
       <c r="D74">
-        <v>12.7149582310742</v>
+        <v>12.72968095261525</v>
       </c>
       <c r="E74">
-        <v>-2.754742111062113</v>
+        <v>-2.620287035667038</v>
       </c>
       <c r="F74">
-        <v>9.680765428445433</v>
+        <v>9.815220503840507</v>
       </c>
       <c r="G74">
         <v>1.29</v>
@@ -8706,28 +8706,28 @@
         <v>3.008</v>
       </c>
       <c r="M74">
-        <v>0.5353463281930325</v>
+        <v>0.5427816938623801</v>
       </c>
       <c r="N74">
-        <v>2.472653671806968</v>
+        <v>2.46521830613762</v>
       </c>
       <c r="O74">
-        <v>0.7417961015420903</v>
+        <v>0.7395654918412859</v>
       </c>
       <c r="P74">
-        <v>1.730857570264877</v>
+        <v>1.725652814296334</v>
       </c>
       <c r="Q74">
-        <v>2.346857570264878</v>
+        <v>2.341652814296334</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1851142382164706</v>
+        <v>0.1897211905384438</v>
       </c>
       <c r="T74">
-        <v>3.217418896454286</v>
+        <v>3.323815023982536</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.618792623745036</v>
+        <v>5.541822861775927</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -8752,22 +8752,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07948302144537983</v>
+        <v>0.07926285619014789</v>
       </c>
       <c r="C75">
-        <v>4.204460448774739</v>
+        <v>4.084762229489231</v>
       </c>
       <c r="D75">
-        <v>12.72968095261525</v>
+        <v>12.74443780872481</v>
       </c>
       <c r="E75">
-        <v>-2.620287035667038</v>
+        <v>-2.485831960271963</v>
       </c>
       <c r="F75">
-        <v>9.815220503840507</v>
+        <v>9.949675579235583</v>
       </c>
       <c r="G75">
         <v>1.29</v>
@@ -8788,28 +8788,28 @@
         <v>3.008</v>
       </c>
       <c r="M75">
-        <v>0.5427816938623801</v>
+        <v>0.5502170595317277</v>
       </c>
       <c r="N75">
-        <v>2.46521830613762</v>
+        <v>2.457782940468272</v>
       </c>
       <c r="O75">
-        <v>0.7395654918412859</v>
+        <v>0.7373348821404816</v>
       </c>
       <c r="P75">
-        <v>1.725652814296334</v>
+        <v>1.72044805832779</v>
       </c>
       <c r="Q75">
-        <v>2.341652814296334</v>
+        <v>2.33644805832779</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1897211905384438</v>
+        <v>0.1946825238082611</v>
       </c>
       <c r="T75">
-        <v>3.323815023982536</v>
+        <v>3.438395469012959</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -8826,7 +8826,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.541822861775927</v>
+        <v>5.466933363643819</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -8834,22 +8834,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07926285619014789</v>
+        <v>0.07904269093491596</v>
       </c>
       <c r="C76">
-        <v>4.084762229489231</v>
+        <v>3.965098263621297</v>
       </c>
       <c r="D76">
-        <v>12.74443780872481</v>
+        <v>12.75922891825195</v>
       </c>
       <c r="E76">
-        <v>-2.485831960271963</v>
+        <v>-2.351376884876887</v>
       </c>
       <c r="F76">
-        <v>9.949675579235583</v>
+        <v>10.08413065463066</v>
       </c>
       <c r="G76">
         <v>1.29</v>
@@ -8870,28 +8870,28 @@
         <v>3.008</v>
       </c>
       <c r="M76">
-        <v>0.5502170595317277</v>
+        <v>0.5576524252010755</v>
       </c>
       <c r="N76">
-        <v>2.457782940468272</v>
+        <v>2.450347574798925</v>
       </c>
       <c r="O76">
-        <v>0.7373348821404816</v>
+        <v>0.7351042724396774</v>
       </c>
       <c r="P76">
-        <v>1.72044805832779</v>
+        <v>1.715243302359247</v>
       </c>
       <c r="Q76">
-        <v>2.33644805832779</v>
+        <v>2.331243302359248</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1946825238082611</v>
+        <v>0.2000407637396638</v>
       </c>
       <c r="T76">
-        <v>3.438395469012959</v>
+        <v>3.562142349645816</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -8908,7 +8908,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.466933363643819</v>
+        <v>5.394040918795235</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8916,22 +8916,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07904269093491596</v>
+        <v>0.07882252567968404</v>
       </c>
       <c r="C77">
-        <v>3.965098263621297</v>
+        <v>3.845468670572368</v>
       </c>
       <c r="D77">
-        <v>12.75922891825195</v>
+        <v>12.7740544005981</v>
       </c>
       <c r="E77">
-        <v>-2.351376884876887</v>
+        <v>-2.216921809481811</v>
       </c>
       <c r="F77">
-        <v>10.08413065463066</v>
+        <v>10.21858573002574</v>
       </c>
       <c r="G77">
         <v>1.29</v>
@@ -8952,28 +8952,28 @@
         <v>3.008</v>
       </c>
       <c r="M77">
-        <v>0.5576524252010755</v>
+        <v>0.5650877908704232</v>
       </c>
       <c r="N77">
-        <v>2.450347574798925</v>
+        <v>2.442912209129577</v>
       </c>
       <c r="O77">
-        <v>0.7351042724396774</v>
+        <v>0.7328736627388731</v>
       </c>
       <c r="P77">
-        <v>1.715243302359247</v>
+        <v>1.710038546390704</v>
       </c>
       <c r="Q77">
-        <v>2.331243302359248</v>
+        <v>2.326038546390704</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2000407637396638</v>
+        <v>0.2058455236653502</v>
       </c>
       <c r="T77">
-        <v>3.562142349645816</v>
+        <v>3.696201470331412</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -8990,7 +8990,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.394040918795235</v>
+        <v>5.323066696179508</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8998,22 +8998,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07882252567968404</v>
+        <v>0.07860236042445211</v>
       </c>
       <c r="C78">
-        <v>3.845468670572368</v>
+        <v>3.725873570299495</v>
       </c>
       <c r="D78">
-        <v>12.7740544005981</v>
+        <v>12.7889143757203</v>
       </c>
       <c r="E78">
-        <v>-2.216921809481811</v>
+        <v>-2.082466734086735</v>
       </c>
       <c r="F78">
-        <v>10.21858573002574</v>
+        <v>10.35304080542081</v>
       </c>
       <c r="G78">
         <v>1.29</v>
@@ -9034,28 +9034,28 @@
         <v>3.008</v>
       </c>
       <c r="M78">
-        <v>0.5650877908704232</v>
+        <v>0.5725231565397708</v>
       </c>
       <c r="N78">
-        <v>2.442912209129577</v>
+        <v>2.435476843460229</v>
       </c>
       <c r="O78">
-        <v>0.7328736627388731</v>
+        <v>0.7306430530380688</v>
       </c>
       <c r="P78">
-        <v>1.710038546390704</v>
+        <v>1.70483379042216</v>
       </c>
       <c r="Q78">
-        <v>2.326038546390704</v>
+        <v>2.320833790422161</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2058455236653502</v>
+        <v>0.2121550453237048</v>
       </c>
       <c r="T78">
-        <v>3.696201470331412</v>
+        <v>3.841917905859233</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.323066696179508</v>
+        <v>5.253935959865489</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -9080,22 +9080,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07860236042445211</v>
+        <v>0.07838219516922017</v>
       </c>
       <c r="C79">
-        <v>3.725873570299495</v>
+        <v>3.606313083318536</v>
       </c>
       <c r="D79">
-        <v>12.7889143757203</v>
+        <v>12.80380896413442</v>
       </c>
       <c r="E79">
-        <v>-2.082466734086735</v>
+        <v>-1.94801165869166</v>
       </c>
       <c r="F79">
-        <v>10.35304080542081</v>
+        <v>10.48749588081589</v>
       </c>
       <c r="G79">
         <v>1.29</v>
@@ -9116,28 +9116,28 @@
         <v>3.008</v>
       </c>
       <c r="M79">
-        <v>0.5725231565397708</v>
+        <v>0.5799585222091185</v>
       </c>
       <c r="N79">
-        <v>2.435476843460229</v>
+        <v>2.428041477790881</v>
       </c>
       <c r="O79">
-        <v>0.7306430530380688</v>
+        <v>0.7284124433372644</v>
       </c>
       <c r="P79">
-        <v>1.70483379042216</v>
+        <v>1.699629034453617</v>
       </c>
       <c r="Q79">
-        <v>2.320833790422161</v>
+        <v>2.315629034453617</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2121550453237048</v>
+        <v>0.2190381598600917</v>
       </c>
       <c r="T79">
-        <v>3.841917905859233</v>
+        <v>4.000881290071401</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.253935959865489</v>
+        <v>5.186577806533879</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -9162,22 +9162,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07838219516922017</v>
+        <v>0.07816202991398824</v>
       </c>
       <c r="C80">
-        <v>3.606313083318536</v>
+        <v>3.486787330707449</v>
       </c>
       <c r="D80">
-        <v>12.80380896413442</v>
+        <v>12.81873828691841</v>
       </c>
       <c r="E80">
-        <v>-1.94801165869166</v>
+        <v>-1.813556583296585</v>
       </c>
       <c r="F80">
-        <v>10.48749588081589</v>
+        <v>10.62195095621096</v>
       </c>
       <c r="G80">
         <v>1.29</v>
@@ -9198,28 +9198,28 @@
         <v>3.008</v>
       </c>
       <c r="M80">
-        <v>0.5799585222091185</v>
+        <v>0.5873938878784661</v>
       </c>
       <c r="N80">
-        <v>2.428041477790881</v>
+        <v>2.420606112121534</v>
       </c>
       <c r="O80">
-        <v>0.7284124433372644</v>
+        <v>0.7261818336364601</v>
       </c>
       <c r="P80">
-        <v>1.699629034453617</v>
+        <v>1.694424278485074</v>
       </c>
       <c r="Q80">
-        <v>2.315629034453617</v>
+        <v>2.310424278485073</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2190381598600917</v>
+        <v>0.2265768091142297</v>
       </c>
       <c r="T80">
-        <v>4.000881290071401</v>
+        <v>4.174984044208538</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -9236,7 +9236,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.186577806533879</v>
+        <v>5.120924922906868</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -9244,22 +9244,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07816202991398824</v>
+        <v>0.0779418646587563</v>
       </c>
       <c r="C81">
-        <v>3.486787330707449</v>
+        <v>3.367296434109562</v>
       </c>
       <c r="D81">
-        <v>12.81873828691841</v>
+        <v>12.8337024657156</v>
       </c>
       <c r="E81">
-        <v>-1.813556583296585</v>
+        <v>-1.679101507901509</v>
       </c>
       <c r="F81">
-        <v>10.62195095621096</v>
+        <v>10.75640603160604</v>
       </c>
       <c r="G81">
         <v>1.29</v>
@@ -9280,28 +9280,28 @@
         <v>3.008</v>
       </c>
       <c r="M81">
-        <v>0.5873938878784661</v>
+        <v>0.5948292535478139</v>
       </c>
       <c r="N81">
-        <v>2.420606112121534</v>
+        <v>2.413170746452186</v>
       </c>
       <c r="O81">
-        <v>0.7261818336364601</v>
+        <v>0.7239512239356559</v>
       </c>
       <c r="P81">
-        <v>1.694424278485074</v>
+        <v>1.689219522516531</v>
       </c>
       <c r="Q81">
-        <v>2.310424278485073</v>
+        <v>2.305219522516531</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2265768091142297</v>
+        <v>0.2348693232937815</v>
       </c>
       <c r="T81">
-        <v>4.174984044208538</v>
+        <v>4.366497073759389</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -9318,7 +9318,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.120924922906868</v>
+        <v>5.056913361370532</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -9326,22 +9326,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0779418646587563</v>
+        <v>0.07772169940352436</v>
       </c>
       <c r="C82">
-        <v>3.367296434109562</v>
+        <v>3.247840515736874</v>
       </c>
       <c r="D82">
-        <v>12.8337024657156</v>
+        <v>12.84870162273799</v>
       </c>
       <c r="E82">
-        <v>-1.679101507901509</v>
+        <v>-1.544646432506433</v>
       </c>
       <c r="F82">
-        <v>10.75640603160604</v>
+        <v>10.89086110700111</v>
       </c>
       <c r="G82">
         <v>1.29</v>
@@ -9362,28 +9362,28 @@
         <v>3.008</v>
       </c>
       <c r="M82">
-        <v>0.5948292535478139</v>
+        <v>0.6022646192171616</v>
       </c>
       <c r="N82">
-        <v>2.413170746452186</v>
+        <v>2.405735380782839</v>
       </c>
       <c r="O82">
-        <v>0.7239512239356559</v>
+        <v>0.7217206142348516</v>
       </c>
       <c r="P82">
-        <v>1.689219522516531</v>
+        <v>1.684014766547987</v>
       </c>
       <c r="Q82">
-        <v>2.305219522516531</v>
+        <v>2.300014766547987</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2348693232937815</v>
+        <v>0.2440347337027599</v>
       </c>
       <c r="T82">
-        <v>4.366497073759389</v>
+        <v>4.57816936957875</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -9400,7 +9400,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.056913361370532</v>
+        <v>4.994482332217809</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -9408,22 +9408,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07772169940352436</v>
+        <v>0.07750153414829243</v>
       </c>
       <c r="C83">
-        <v>3.247840515736874</v>
+        <v>3.128419698373385</v>
       </c>
       <c r="D83">
-        <v>12.84870162273799</v>
+        <v>12.86373588076957</v>
       </c>
       <c r="E83">
-        <v>-1.544646432506433</v>
+        <v>-1.410191357111357</v>
       </c>
       <c r="F83">
-        <v>10.89086110700111</v>
+        <v>11.02531618239619</v>
       </c>
       <c r="G83">
         <v>1.29</v>
@@ -9444,28 +9444,28 @@
         <v>3.008</v>
       </c>
       <c r="M83">
-        <v>0.6022646192171616</v>
+        <v>0.6096999848865092</v>
       </c>
       <c r="N83">
-        <v>2.405735380782839</v>
+        <v>2.398300015113491</v>
       </c>
       <c r="O83">
-        <v>0.7217206142348516</v>
+        <v>0.7194900045340472</v>
       </c>
       <c r="P83">
-        <v>1.684014766547987</v>
+        <v>1.678810010579443</v>
       </c>
       <c r="Q83">
-        <v>2.300014766547987</v>
+        <v>2.294810010579444</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2440347337027599</v>
+        <v>0.2542185230460691</v>
       </c>
       <c r="T83">
-        <v>4.57816936957875</v>
+        <v>4.81336080937804</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.994482332217809</v>
+        <v>4.933574011093202</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -9490,22 +9490,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07750153414829243</v>
+        <v>0.0772813688930605</v>
       </c>
       <c r="C84">
-        <v>3.128419698373385</v>
+        <v>3.009034105378447</v>
       </c>
       <c r="D84">
-        <v>12.86373588076957</v>
+        <v>12.87880536316971</v>
       </c>
       <c r="E84">
-        <v>-1.410191357111357</v>
+        <v>-1.275736281716283</v>
       </c>
       <c r="F84">
-        <v>11.02531618239619</v>
+        <v>11.15977125779126</v>
       </c>
       <c r="G84">
         <v>1.29</v>
@@ -9526,28 +9526,28 @@
         <v>3.008</v>
       </c>
       <c r="M84">
-        <v>0.6096999848865092</v>
+        <v>0.6171353505558569</v>
       </c>
       <c r="N84">
-        <v>2.398300015113491</v>
+        <v>2.390864649444143</v>
       </c>
       <c r="O84">
-        <v>0.7194900045340472</v>
+        <v>0.7172593948332429</v>
       </c>
       <c r="P84">
-        <v>1.678810010579443</v>
+        <v>1.6736052546109</v>
       </c>
       <c r="Q84">
-        <v>2.294810010579444</v>
+        <v>2.2896052546109</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2542185230460691</v>
+        <v>0.2656004052532971</v>
       </c>
       <c r="T84">
-        <v>4.81336080937804</v>
+        <v>5.076221830330188</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.933574011093202</v>
+        <v>4.874133360357139</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -9572,22 +9572,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0772813688930605</v>
+        <v>0.07706120363782856</v>
       </c>
       <c r="C85">
-        <v>3.009034105378447</v>
+        <v>2.889683860690139</v>
       </c>
       <c r="D85">
-        <v>12.87880536316971</v>
+        <v>12.89391019387648</v>
       </c>
       <c r="E85">
-        <v>-1.275736281716283</v>
+        <v>-1.141281206321207</v>
       </c>
       <c r="F85">
-        <v>11.15977125779126</v>
+        <v>11.29422633318634</v>
       </c>
       <c r="G85">
         <v>1.29</v>
@@ -9608,28 +9608,28 @@
         <v>3.008</v>
       </c>
       <c r="M85">
-        <v>0.6171353505558569</v>
+        <v>0.6245707162252045</v>
       </c>
       <c r="N85">
-        <v>2.390864649444143</v>
+        <v>2.383429283774795</v>
       </c>
       <c r="O85">
-        <v>0.7172593948332429</v>
+        <v>0.7150287851324385</v>
       </c>
       <c r="P85">
-        <v>1.6736052546109</v>
+        <v>1.668400498642357</v>
       </c>
       <c r="Q85">
-        <v>2.2896052546109</v>
+        <v>2.284400498642357</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2656004052532971</v>
+        <v>0.2784050227364287</v>
       </c>
       <c r="T85">
-        <v>5.076221830330188</v>
+        <v>5.371940478901355</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -9646,7 +9646,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.874133360357139</v>
+        <v>4.816107963210031</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -9654,22 +9654,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07706120363782858</v>
+        <v>0.07684103838259665</v>
       </c>
       <c r="C86">
-        <v>2.889683860690141</v>
+        <v>2.770369088828661</v>
       </c>
       <c r="D86">
-        <v>12.89391019387648</v>
+        <v>12.90905049741007</v>
       </c>
       <c r="E86">
-        <v>-1.141281206321208</v>
+        <v>-1.006826130926132</v>
       </c>
       <c r="F86">
-        <v>11.29422633318634</v>
+        <v>11.42868140858141</v>
       </c>
       <c r="G86">
         <v>1.29</v>
@@ -9690,28 +9690,28 @@
         <v>3.008</v>
       </c>
       <c r="M86">
-        <v>0.6245707162252044</v>
+        <v>0.6320060818945522</v>
       </c>
       <c r="N86">
-        <v>2.383429283774796</v>
+        <v>2.375993918105448</v>
       </c>
       <c r="O86">
-        <v>0.7150287851324387</v>
+        <v>0.7127981754316344</v>
       </c>
       <c r="P86">
-        <v>1.668400498642357</v>
+        <v>1.663195742673814</v>
       </c>
       <c r="Q86">
-        <v>2.284400498642357</v>
+        <v>2.279195742673814</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2784050227364285</v>
+        <v>0.2929169225506442</v>
       </c>
       <c r="T86">
-        <v>5.371940478901352</v>
+        <v>5.70708828061534</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.816107963210031</v>
+        <v>4.759447869525207</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -9736,22 +9736,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07684103838259665</v>
+        <v>0.07662087312736471</v>
       </c>
       <c r="C87">
-        <v>2.770369088828661</v>
+        <v>2.651089914899753</v>
       </c>
       <c r="D87">
-        <v>12.90905049741007</v>
+        <v>12.92422639887624</v>
       </c>
       <c r="E87">
-        <v>-1.006826130926132</v>
+        <v>-0.8723710555310564</v>
       </c>
       <c r="F87">
-        <v>11.42868140858141</v>
+        <v>11.56313648397649</v>
       </c>
       <c r="G87">
         <v>1.29</v>
@@ -9772,28 +9772,28 @@
         <v>3.008</v>
       </c>
       <c r="M87">
-        <v>0.6320060818945522</v>
+        <v>0.6394414475638999</v>
       </c>
       <c r="N87">
-        <v>2.375993918105448</v>
+        <v>2.3685585524361</v>
       </c>
       <c r="O87">
-        <v>0.7127981754316344</v>
+        <v>0.71056756573083</v>
       </c>
       <c r="P87">
-        <v>1.663195742673814</v>
+        <v>1.65799098670527</v>
       </c>
       <c r="Q87">
-        <v>2.279195742673814</v>
+        <v>2.27399098670527</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2929169225506442</v>
+        <v>0.3095019509097479</v>
       </c>
       <c r="T87">
-        <v>5.70708828061534</v>
+        <v>6.09011433971704</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.759447869525207</v>
+        <v>4.704105452437705</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -9818,22 +9818,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07662087312736471</v>
+        <v>0.07640070787213277</v>
       </c>
       <c r="C88">
-        <v>2.651089914899753</v>
+        <v>2.531846464598152</v>
       </c>
       <c r="D88">
-        <v>12.92422639887624</v>
+        <v>12.93943802396972</v>
       </c>
       <c r="E88">
-        <v>-0.8723710555310564</v>
+        <v>-0.7379159801359805</v>
       </c>
       <c r="F88">
-        <v>11.56313648397649</v>
+        <v>11.69759155937157</v>
       </c>
       <c r="G88">
         <v>1.29</v>
@@ -9854,28 +9854,28 @@
         <v>3.008</v>
       </c>
       <c r="M88">
-        <v>0.6394414475638999</v>
+        <v>0.6468768132332475</v>
       </c>
       <c r="N88">
-        <v>2.3685585524361</v>
+        <v>2.361123186766752</v>
       </c>
       <c r="O88">
-        <v>0.71056756573083</v>
+        <v>0.7083369560300257</v>
       </c>
       <c r="P88">
-        <v>1.65799098670527</v>
+        <v>1.652786230736727</v>
       </c>
       <c r="Q88">
-        <v>2.27399098670527</v>
+        <v>2.268786230736727</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3095019509097479</v>
+        <v>0.328638522093329</v>
       </c>
       <c r="T88">
-        <v>6.09011433971704</v>
+        <v>6.532067484834388</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.704105452437705</v>
+        <v>4.650035274823479</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9900,22 +9900,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07640070787213277</v>
+        <v>0.07618054261690084</v>
       </c>
       <c r="C89">
-        <v>2.531846464598152</v>
+        <v>2.412638864211056</v>
       </c>
       <c r="D89">
-        <v>12.93943802396972</v>
+        <v>12.9546854989777</v>
       </c>
       <c r="E89">
-        <v>-0.7379159801359805</v>
+        <v>-0.6034609047409063</v>
       </c>
       <c r="F89">
-        <v>11.69759155937157</v>
+        <v>11.83204663476664</v>
       </c>
       <c r="G89">
         <v>1.29</v>
@@ -9936,28 +9936,28 @@
         <v>3.008</v>
       </c>
       <c r="M89">
-        <v>0.6468768132332475</v>
+        <v>0.6543121789025952</v>
       </c>
       <c r="N89">
-        <v>2.361123186766752</v>
+        <v>2.353687821097405</v>
       </c>
       <c r="O89">
-        <v>0.7083369560300257</v>
+        <v>0.7061063463292215</v>
       </c>
       <c r="P89">
-        <v>1.652786230736727</v>
+        <v>1.647581474768184</v>
       </c>
       <c r="Q89">
-        <v>2.268786230736727</v>
+        <v>2.263581474768184</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.328638522093329</v>
+        <v>0.350964521807507</v>
       </c>
       <c r="T89">
-        <v>6.532067484834388</v>
+        <v>7.047679487471294</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -9974,7 +9974,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.650035274823479</v>
+        <v>4.597193964882303</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9982,22 +9982,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07618054261690084</v>
+        <v>0.07596037736166891</v>
       </c>
       <c r="C90">
-        <v>2.412638864211056</v>
+        <v>2.293467240621613</v>
       </c>
       <c r="D90">
-        <v>12.9546854989777</v>
+        <v>12.96996895078333</v>
       </c>
       <c r="E90">
-        <v>-0.6034609047409063</v>
+        <v>-0.4690058293458303</v>
       </c>
       <c r="F90">
-        <v>11.83204663476664</v>
+        <v>11.96650171016172</v>
       </c>
       <c r="G90">
         <v>1.29</v>
@@ -10018,28 +10018,28 @@
         <v>3.008</v>
       </c>
       <c r="M90">
-        <v>0.6543121789025952</v>
+        <v>0.6617475445719428</v>
       </c>
       <c r="N90">
-        <v>2.353687821097405</v>
+        <v>2.346252455428057</v>
       </c>
       <c r="O90">
-        <v>0.7061063463292215</v>
+        <v>0.7038757366284172</v>
       </c>
       <c r="P90">
-        <v>1.647581474768184</v>
+        <v>1.64237671879964</v>
       </c>
       <c r="Q90">
-        <v>2.263581474768184</v>
+        <v>2.25837671879964</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.350964521807507</v>
+        <v>0.3773497941969901</v>
       </c>
       <c r="T90">
-        <v>7.047679487471294</v>
+        <v>7.657039126951273</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -10056,7 +10056,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.597193964882303</v>
+        <v>4.545540100108344</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -10064,22 +10064,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07596037736166891</v>
+        <v>0.07731521210643696</v>
       </c>
       <c r="C91">
-        <v>2.293467240621613</v>
+        <v>2.06552984104446</v>
       </c>
       <c r="D91">
-        <v>12.96996895078333</v>
+        <v>12.87648662660125</v>
       </c>
       <c r="E91">
-        <v>-0.4690058293458303</v>
+        <v>-0.3345507539507544</v>
       </c>
       <c r="F91">
-        <v>11.96650171016172</v>
+        <v>12.10095678555679</v>
       </c>
       <c r="G91">
         <v>1.29</v>
@@ -10100,45 +10100,45 @@
         <v>3.008</v>
       </c>
       <c r="M91">
-        <v>0.6617475445719428</v>
+        <v>0.6994353022051826</v>
       </c>
       <c r="N91">
-        <v>2.346252455428057</v>
+        <v>2.308564697794818</v>
       </c>
       <c r="O91">
-        <v>0.7038757366284172</v>
+        <v>0.6925694093384452</v>
       </c>
       <c r="P91">
-        <v>1.64237671879964</v>
+        <v>1.615995288456372</v>
       </c>
       <c r="Q91">
-        <v>2.25837671879964</v>
+        <v>2.231995288456373</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3773497941969901</v>
+        <v>0.4090121210643698</v>
       </c>
       <c r="T91">
-        <v>7.657039126951273</v>
+        <v>8.388270694327247</v>
       </c>
       <c r="U91">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V91">
         <v>0.3</v>
       </c>
       <c r="W91">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y91">
-        <v>4.545540100108344</v>
+        <v>4.300612208901045</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -10146,22 +10146,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07731521210643696</v>
+        <v>0.07711254685120504</v>
       </c>
       <c r="C92">
-        <v>2.06552984104446</v>
+        <v>1.944972673006713</v>
       </c>
       <c r="D92">
-        <v>12.87648662660125</v>
+        <v>12.89038453395858</v>
       </c>
       <c r="E92">
-        <v>-0.3345507539507544</v>
+        <v>-0.2000956785556784</v>
       </c>
       <c r="F92">
-        <v>12.10095678555679</v>
+        <v>12.23541186095187</v>
       </c>
       <c r="G92">
         <v>1.29</v>
@@ -10182,28 +10182,28 @@
         <v>3.008</v>
       </c>
       <c r="M92">
-        <v>0.6994353022051826</v>
+        <v>0.707206805563018</v>
       </c>
       <c r="N92">
-        <v>2.308564697794818</v>
+        <v>2.300793194436982</v>
       </c>
       <c r="O92">
-        <v>0.6925694093384452</v>
+        <v>0.6902379583310946</v>
       </c>
       <c r="P92">
-        <v>1.615995288456372</v>
+        <v>1.610555236105887</v>
       </c>
       <c r="Q92">
-        <v>2.231995288456373</v>
+        <v>2.226555236105888</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4090121210643698</v>
+        <v>0.447710520568945</v>
       </c>
       <c r="T92">
-        <v>8.388270694327247</v>
+        <v>9.28199816556455</v>
       </c>
       <c r="U92">
         <v>0.0578</v>
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.300612208901045</v>
+        <v>4.253352734077956</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -10228,22 +10228,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07711254685120504</v>
+        <v>0.07690988159597312</v>
       </c>
       <c r="C93">
-        <v>1.944972673006713</v>
+        <v>1.82444553808798</v>
       </c>
       <c r="D93">
-        <v>12.89038453395858</v>
+        <v>12.90431247443492</v>
       </c>
       <c r="E93">
-        <v>-0.2000956785556784</v>
+        <v>-0.0656406031606025</v>
       </c>
       <c r="F93">
-        <v>12.23541186095187</v>
+        <v>12.36986693634694</v>
       </c>
       <c r="G93">
         <v>1.29</v>
@@ -10264,28 +10264,28 @@
         <v>3.008</v>
       </c>
       <c r="M93">
-        <v>0.707206805563018</v>
+        <v>0.7149783089208533</v>
       </c>
       <c r="N93">
-        <v>2.300793194436982</v>
+        <v>2.293021691079147</v>
       </c>
       <c r="O93">
-        <v>0.6902379583310946</v>
+        <v>0.687906507323744</v>
       </c>
       <c r="P93">
-        <v>1.610555236105887</v>
+        <v>1.605115183755403</v>
       </c>
       <c r="Q93">
-        <v>2.226555236105888</v>
+        <v>2.221115183755403</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.447710520568945</v>
+        <v>0.4960835199496641</v>
       </c>
       <c r="T93">
-        <v>9.28199816556455</v>
+        <v>10.39915750461118</v>
       </c>
       <c r="U93">
         <v>0.0578</v>
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.253352734077956</v>
+        <v>4.207120639142326</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -10310,22 +10310,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07690988159597312</v>
+        <v>0.07670721634074118</v>
       </c>
       <c r="C94">
-        <v>1.82444553808798</v>
+        <v>1.703948533745079</v>
       </c>
       <c r="D94">
-        <v>12.90431247443492</v>
+        <v>12.9182705454871</v>
       </c>
       <c r="E94">
-        <v>-0.0656406031606025</v>
+        <v>0.06881447223447168</v>
       </c>
       <c r="F94">
-        <v>12.36986693634694</v>
+        <v>12.50432201174202</v>
       </c>
       <c r="G94">
         <v>1.29</v>
@@ -10346,28 +10346,28 @@
         <v>3.008</v>
       </c>
       <c r="M94">
-        <v>0.7149783089208533</v>
+        <v>0.7227498122786886</v>
       </c>
       <c r="N94">
-        <v>2.293021691079147</v>
+        <v>2.285250187721311</v>
       </c>
       <c r="O94">
-        <v>0.687906507323744</v>
+        <v>0.6855750563163934</v>
       </c>
       <c r="P94">
-        <v>1.605115183755403</v>
+        <v>1.599675131404918</v>
       </c>
       <c r="Q94">
-        <v>2.221115183755403</v>
+        <v>2.215675131404918</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4960835199496641</v>
+        <v>0.5582773762963028</v>
       </c>
       <c r="T94">
-        <v>10.39915750461118</v>
+        <v>11.83550522624256</v>
       </c>
       <c r="U94">
         <v>0.0578</v>
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.207120639142326</v>
+        <v>4.161882782807463</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -10392,22 +10392,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07670721634074118</v>
+        <v>0.07650455108550924</v>
       </c>
       <c r="C95">
-        <v>1.703948533745079</v>
+        <v>1.583481757856941</v>
       </c>
       <c r="D95">
-        <v>12.9182705454871</v>
+        <v>12.93225884499403</v>
       </c>
       <c r="E95">
-        <v>0.06881447223447168</v>
+        <v>0.2032695476295476</v>
       </c>
       <c r="F95">
-        <v>12.50432201174202</v>
+        <v>12.63877708713709</v>
       </c>
       <c r="G95">
         <v>1.29</v>
@@ -10428,28 +10428,28 @@
         <v>3.008</v>
       </c>
       <c r="M95">
-        <v>0.7227498122786886</v>
+        <v>0.730521315636524</v>
       </c>
       <c r="N95">
-        <v>2.285250187721311</v>
+        <v>2.277478684363476</v>
       </c>
       <c r="O95">
-        <v>0.6855750563163934</v>
+        <v>0.6832436053090428</v>
       </c>
       <c r="P95">
-        <v>1.599675131404918</v>
+        <v>1.594235079054433</v>
       </c>
       <c r="Q95">
-        <v>2.215675131404918</v>
+        <v>2.210235079054433</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5582773762963028</v>
+        <v>0.6412025180918212</v>
       </c>
       <c r="T95">
-        <v>11.83550522624256</v>
+        <v>13.75063552175107</v>
       </c>
       <c r="U95">
         <v>0.0578</v>
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.161882782807463</v>
+        <v>4.117607434054191</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -10474,22 +10474,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07650455108550924</v>
+        <v>0.07630188583027731</v>
       </c>
       <c r="C96">
-        <v>1.583481757856941</v>
+        <v>1.46304530872691</v>
       </c>
       <c r="D96">
-        <v>12.93225884499403</v>
+        <v>12.94627747125908</v>
       </c>
       <c r="E96">
-        <v>0.2032695476295476</v>
+        <v>0.3377246230246236</v>
       </c>
       <c r="F96">
-        <v>12.63877708713709</v>
+        <v>12.77323216253217</v>
       </c>
       <c r="G96">
         <v>1.29</v>
@@ -10510,28 +10510,28 @@
         <v>3.008</v>
       </c>
       <c r="M96">
-        <v>0.730521315636524</v>
+        <v>0.7382928189943594</v>
       </c>
       <c r="N96">
-        <v>2.277478684363476</v>
+        <v>2.269707181005641</v>
       </c>
       <c r="O96">
-        <v>0.6832436053090428</v>
+        <v>0.6809121543016922</v>
       </c>
       <c r="P96">
-        <v>1.594235079054433</v>
+        <v>1.588795026703949</v>
       </c>
       <c r="Q96">
-        <v>2.210235079054433</v>
+        <v>2.204795026703949</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6412025180918212</v>
+        <v>0.7572977166055471</v>
       </c>
       <c r="T96">
-        <v>13.75063552175107</v>
+        <v>16.43181793546298</v>
       </c>
       <c r="U96">
         <v>0.0578</v>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.117607434054191</v>
+        <v>4.074264197906253</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -10556,22 +10556,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07630188583027731</v>
+        <v>0.07609922057504537</v>
       </c>
       <c r="C97">
-        <v>1.46304530872691</v>
+        <v>1.342639285085028</v>
       </c>
       <c r="D97">
-        <v>12.94627747125908</v>
+        <v>12.96032652301227</v>
       </c>
       <c r="E97">
-        <v>0.3377246230246236</v>
+        <v>0.4721796984196995</v>
       </c>
       <c r="F97">
-        <v>12.77323216253217</v>
+        <v>12.90768723792725</v>
       </c>
       <c r="G97">
         <v>1.29</v>
@@ -10592,28 +10592,28 @@
         <v>3.008</v>
       </c>
       <c r="M97">
-        <v>0.7382928189943594</v>
+        <v>0.7460643223521948</v>
       </c>
       <c r="N97">
-        <v>2.269707181005641</v>
+        <v>2.261935677647805</v>
       </c>
       <c r="O97">
-        <v>0.6809121543016922</v>
+        <v>0.6785807032943415</v>
       </c>
       <c r="P97">
-        <v>1.588795026703949</v>
+        <v>1.583354974353464</v>
       </c>
       <c r="Q97">
-        <v>2.204795026703949</v>
+        <v>2.199354974353464</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7572977166055471</v>
+        <v>0.9314405143761361</v>
       </c>
       <c r="T97">
-        <v>16.43181793546298</v>
+        <v>20.45359155603086</v>
       </c>
       <c r="U97">
         <v>0.0578</v>
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.074264197906253</v>
+        <v>4.03182394584473</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -10638,22 +10638,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07609922057504538</v>
+        <v>0.07827305531981345</v>
       </c>
       <c r="C98">
-        <v>1.342639285085029</v>
+        <v>1.059063033724954</v>
       </c>
       <c r="D98">
-        <v>12.96032652301227</v>
+        <v>12.81120534704727</v>
       </c>
       <c r="E98">
-        <v>0.4721796984196978</v>
+        <v>0.6066347738147737</v>
       </c>
       <c r="F98">
-        <v>12.90768723792724</v>
+        <v>13.04214231332232</v>
       </c>
       <c r="G98">
         <v>1.29</v>
@@ -10674,45 +10674,45 @@
         <v>3.008</v>
       </c>
       <c r="M98">
-        <v>0.7460643223521948</v>
+        <v>0.7994833238066582</v>
       </c>
       <c r="N98">
-        <v>2.261935677647805</v>
+        <v>2.208516676193342</v>
       </c>
       <c r="O98">
-        <v>0.6785807032943415</v>
+        <v>0.6625550028580025</v>
       </c>
       <c r="P98">
-        <v>1.583354974353464</v>
+        <v>1.545961673335339</v>
       </c>
       <c r="Q98">
-        <v>2.199354974353464</v>
+        <v>2.161961673335339</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9314405143761336</v>
+        <v>1.221678510660447</v>
       </c>
       <c r="T98">
-        <v>20.4535915560308</v>
+        <v>27.15654759031056</v>
       </c>
       <c r="U98">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V98">
         <v>0.3</v>
       </c>
       <c r="W98">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y98">
-        <v>4.03182394584473</v>
+        <v>3.762429947478723</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -10720,22 +10720,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07827305531981345</v>
+        <v>0.07809489006458151</v>
       </c>
       <c r="C99">
-        <v>1.059063033724954</v>
+        <v>0.9367005558401118</v>
       </c>
       <c r="D99">
-        <v>12.81120534704727</v>
+        <v>12.82329794455751</v>
       </c>
       <c r="E99">
-        <v>0.6066347738147737</v>
+        <v>0.7410898492098479</v>
       </c>
       <c r="F99">
-        <v>13.04214231332232</v>
+        <v>13.17659738871739</v>
       </c>
       <c r="G99">
         <v>1.29</v>
@@ -10756,28 +10756,28 @@
         <v>3.008</v>
       </c>
       <c r="M99">
-        <v>0.7994833238066582</v>
+        <v>0.8077254199283762</v>
       </c>
       <c r="N99">
-        <v>2.208516676193342</v>
+        <v>2.200274580071624</v>
       </c>
       <c r="O99">
-        <v>0.6625550028580025</v>
+        <v>0.6600823740214872</v>
       </c>
       <c r="P99">
-        <v>1.545961673335339</v>
+        <v>1.540192206050137</v>
       </c>
       <c r="Q99">
-        <v>2.161961673335339</v>
+        <v>2.156192206050137</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.221678510660447</v>
+        <v>1.802154503229074</v>
       </c>
       <c r="T99">
-        <v>27.15654759031056</v>
+        <v>40.56245965887007</v>
       </c>
       <c r="U99">
         <v>0.0613</v>
@@ -10794,7 +10794,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.762429947478723</v>
+        <v>3.724037805157512</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -10802,22 +10802,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07809489006458151</v>
+        <v>0.07791672480934958</v>
       </c>
       <c r="C100">
-        <v>0.9367005558401118</v>
+        <v>0.8143609281195605</v>
       </c>
       <c r="D100">
-        <v>12.82329794455751</v>
+        <v>12.83541339223203</v>
       </c>
       <c r="E100">
-        <v>0.7410898492098479</v>
+        <v>0.8755449246049238</v>
       </c>
       <c r="F100">
-        <v>13.17659738871739</v>
+        <v>13.31105246411247</v>
       </c>
       <c r="G100">
         <v>1.29</v>
@@ -10838,28 +10838,28 @@
         <v>3.008</v>
       </c>
       <c r="M100">
-        <v>0.8077254199283762</v>
+        <v>0.8159675160500944</v>
       </c>
       <c r="N100">
-        <v>2.200274580071624</v>
+        <v>2.192032483949906</v>
       </c>
       <c r="O100">
-        <v>0.6600823740214872</v>
+        <v>0.6576097451849717</v>
       </c>
       <c r="P100">
-        <v>1.540192206050137</v>
+        <v>1.534422738764934</v>
       </c>
       <c r="Q100">
-        <v>2.156192206050137</v>
+        <v>2.150422738764934</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.802154503229074</v>
+        <v>3.543582480934955</v>
       </c>
       <c r="T100">
-        <v>40.56245965887007</v>
+        <v>80.78019586454862</v>
       </c>
       <c r="U100">
         <v>0.0613</v>
@@ -10876,91 +10876,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.724037805157512</v>
+        <v>3.686421261671073</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07791672480934958</v>
-      </c>
-      <c r="C101">
-        <v>0.8143609281195605</v>
-      </c>
-      <c r="D101">
-        <v>12.83541339223203</v>
-      </c>
-      <c r="E101">
-        <v>0.8755449246049238</v>
-      </c>
-      <c r="F101">
-        <v>13.31105246411247</v>
-      </c>
-      <c r="G101">
-        <v>1.29</v>
-      </c>
-      <c r="H101">
-        <v>1.01</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.624</v>
-      </c>
-      <c r="K101">
-        <v>0.616</v>
-      </c>
-      <c r="L101">
-        <v>3.008</v>
-      </c>
-      <c r="M101">
-        <v>0.8159675160500944</v>
-      </c>
-      <c r="N101">
-        <v>2.192032483949906</v>
-      </c>
-      <c r="O101">
-        <v>0.6576097451849717</v>
-      </c>
-      <c r="P101">
-        <v>1.534422738764934</v>
-      </c>
-      <c r="Q101">
-        <v>2.150422738764934</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.543582480934955</v>
-      </c>
-      <c r="T101">
-        <v>80.78019586454862</v>
-      </c>
-      <c r="U101">
-        <v>0.0613</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.04291</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba1/BB+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.686421261671073</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
